--- a/db/mm.brain.xlsx
+++ b/db/mm.brain.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/seurat_rds/public_version/v0.2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/seurat_rds/public_version/v0.3/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799BA685-0326-234E-9825-211E3B4DCD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB69A4F3-E749-8445-A2E7-EF585726C926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8600" yWindow="1480" windowWidth="23040" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="492">
   <si>
     <t>tissueType</t>
   </si>
@@ -165,21 +164,12 @@
     <t>Vwa1,Cldn5,Epas1,Col6a1,Ly6c1,Adgrl4</t>
   </si>
   <si>
-    <t>Vas7</t>
-  </si>
-  <si>
-    <t>Esam,Cldn5,Slc27a1,Hmgcs2,Ecscr,Ctla2a</t>
-  </si>
-  <si>
     <t>Kcnj8,Rgs5,Ndufa4l2,Aspn,Tbxa2r,Gper1</t>
   </si>
   <si>
     <t>Pericyte</t>
   </si>
   <si>
-    <t>Foxs1,Kcnj8,Rgs5,Dmp1,Itga1</t>
-  </si>
-  <si>
     <t>VSM1</t>
   </si>
   <si>
@@ -267,12 +257,6 @@
     <t>Blood</t>
   </si>
   <si>
-    <t>Blood8</t>
-  </si>
-  <si>
-    <t>Hbb-bt,Blvrb,Snca,Gad1,Fech,Hbb-bs</t>
-  </si>
-  <si>
     <t>Blood10</t>
   </si>
   <si>
@@ -300,33 +284,6 @@
     <t>Pklr,Ermap,Car1,Nxpe2,Cldn13</t>
   </si>
   <si>
-    <t>Erythroid progenitor</t>
-  </si>
-  <si>
-    <t>B.EryProg2</t>
-  </si>
-  <si>
-    <t>Cited4,Pklr,Smim1,Csf2rb,Hbb-bh1,Klf1</t>
-  </si>
-  <si>
-    <t>B.EryProg3</t>
-  </si>
-  <si>
-    <t>Acp5,Cited4,Dnaja4,Pklr,Klf1,Hbb-bh1</t>
-  </si>
-  <si>
-    <t>B.EryProg4</t>
-  </si>
-  <si>
-    <t>Gm43661,Pdzk1ip1,Ncf4,Kel,Hsd3b6,Hba-x</t>
-  </si>
-  <si>
-    <t>B.EryProg5</t>
-  </si>
-  <si>
-    <t>Rnf212,Hbq1b,Hemgn,Rhd,Icam4,Hba-x</t>
-  </si>
-  <si>
     <t>Blood11</t>
   </si>
   <si>
@@ -375,33 +332,6 @@
     <t>Perivascular fibroblast-like cells</t>
   </si>
   <si>
-    <t>F.Pia1</t>
-  </si>
-  <si>
-    <t>A2m,Col6a2,Dcn,Cxcl16,Kcne4,Olfml3</t>
-  </si>
-  <si>
-    <t>Pia 1</t>
-  </si>
-  <si>
-    <t>F.Pia2</t>
-  </si>
-  <si>
-    <t>Itih5,Gm30624,S100a6,Nupr1,Slc6a13,Adra1a</t>
-  </si>
-  <si>
-    <t>Pia 2</t>
-  </si>
-  <si>
-    <t>F.Pia3</t>
-  </si>
-  <si>
-    <t>Lrrc17,Col6a2,Dcn,Cxcl12,Apod,C1qtnf7</t>
-  </si>
-  <si>
-    <t>Pia 3</t>
-  </si>
-  <si>
     <t>F.Meninges1</t>
   </si>
   <si>
@@ -489,12 +419,6 @@
     <t>Early macrophage</t>
   </si>
   <si>
-    <t>Immune6</t>
-  </si>
-  <si>
-    <t>Cd86,Pf4,Rarres2,Cd14,Ccl24,Ms4a7</t>
-  </si>
-  <si>
     <t>Neutroph</t>
   </si>
   <si>
@@ -555,9 +479,6 @@
     <t>Neuroblast</t>
   </si>
   <si>
-    <t>Pericyte2</t>
-  </si>
-  <si>
     <t>Pericyte1</t>
   </si>
   <si>
@@ -603,18 +524,9 @@
     <t>Forebrain</t>
   </si>
   <si>
-    <t>Mt3,Gm28175,Cbs,Smpdl3a,Baalc,Adhfe1</t>
-  </si>
-  <si>
-    <t>Forebrain astrocyte</t>
-  </si>
-  <si>
     <t>Gm29260,Igfbp4,Rgcc,Megf10,Napepld,Ddah1</t>
   </si>
   <si>
-    <t>Mt3,H19,Ptx3,Lipg,Aspm,Cdkn3</t>
-  </si>
-  <si>
     <t>Gm29260,Lrp4,Htra1,Tmem132b,Gm11627,Rgs20</t>
   </si>
   <si>
@@ -639,9 +551,6 @@
     <t>Forebrain glutamatergic</t>
   </si>
   <si>
-    <t>Dlk1,Crb1,G0s2,Zc3h12c,Btg2,Srrm4</t>
-  </si>
-  <si>
     <t>Gsx1,Crb1,St18,Stk33,Pak3,Peg3</t>
   </si>
   <si>
@@ -669,9 +578,6 @@
     <t>Unc5d,Gm20687,Kcnn3,Foxg1,Nrp1,Cttnbp2</t>
   </si>
   <si>
-    <t>Unc5d,Focad,Cdh10,Galnt17,Nrg1,Cttnbp2</t>
-  </si>
-  <si>
     <t>Gm28050,Hs3st1,Sorl1,Negr1,Tmem108,Pam</t>
   </si>
   <si>
@@ -690,9 +596,6 @@
     <t>Gsx2,Dusp10,Ascl1,Stk33,E2f1,Ccne2</t>
   </si>
   <si>
-    <t>Dlx2,E2f2,Rbm3,Uba52,Ccnd2,Slbp</t>
-  </si>
-  <si>
     <t>Dlx2,Rbl1,Arx,Rffl,Gm10282,Atad2</t>
   </si>
   <si>
@@ -702,18 +605,9 @@
     <t>Dlx6os1,Tmem98,Arx,Zswim5,Grik3,Dclk2</t>
   </si>
   <si>
-    <t>Dlx6os1,Arhgef39,Dlx5,Cep55,Aspm,Sgo2a</t>
-  </si>
-  <si>
-    <t>Gsx2,Gpbp1l1,Dlx5,Stk33,Aspm,Pbk</t>
-  </si>
-  <si>
     <t>Dlx6os1,Sall1,Dlx5,Gm13889,Ccnd2,Nusap1</t>
   </si>
   <si>
-    <t>B020031H02Rik,Arl4d,Dlx5,Gm13889,Ccnd2,Gm14964</t>
-  </si>
-  <si>
     <t>Syt6,Timm23,Ptprm,Bcl11b,Grik3,Kcnd3</t>
   </si>
   <si>
@@ -723,21 +617,12 @@
     <t>Gucy1a1,Zfp385b,Slit3,Bcl11b,Grik3,Lrfn2</t>
   </si>
   <si>
-    <t>Neur531</t>
-  </si>
-  <si>
     <t>B020031H02Rik,Hs6st3,Six3,Bcl11b,Carmil1,Enox1</t>
   </si>
   <si>
-    <t>B020031H02Rik,Angpt1,Gad2,Zfp503,Mpped2,Meis2</t>
-  </si>
-  <si>
     <t>B020031H02Rik,Fam83d,Six3,Mxd3,Aspm,Sgo2a</t>
   </si>
   <si>
-    <t>Calb2,Sp8,Synpr,Brinp1,Kirrel3,Fam124a</t>
-  </si>
-  <si>
     <t>Dlx6os1,Gm38505,Brinp2,Shtn1,Grik3,Zfp704</t>
   </si>
   <si>
@@ -750,9 +635,6 @@
     <t>Cpne4,Gpr26,Gng4,Ano4,Il1rapl1,Otud7a</t>
   </si>
   <si>
-    <t>Dlx1as,Skida1,Arx,Prox1os,Fign,Tmem169</t>
-  </si>
-  <si>
     <t>Dlx6os1,Fgd5,Dlx5,Nrxn3,Slco3a1,Klhdc8b</t>
   </si>
   <si>
@@ -780,9 +662,6 @@
     <t>Rxrg,Gm44593,Trpc7,Lingo2,Foxp1,Rasgef1b</t>
   </si>
   <si>
-    <t>Cntnap3,Ikzf1,Cntn5,Lingo2,Ano3,Rasgef1b</t>
-  </si>
-  <si>
     <t>Rarb,Rell2,Cntn5,Vstm2a,Ano3,Med12l</t>
   </si>
   <si>
@@ -816,9 +695,6 @@
     <t>Nxph2,Dgkg,Gria1,Ptchd4,Gm45881,Dlgap1</t>
   </si>
   <si>
-    <t>Sst,Fam135b,Fam222a,Sox6,Gm45881,Dlgap1</t>
-  </si>
-  <si>
     <t>Npy,Sntg2,Grin3a,Nell1,Ptprt,Klf5</t>
   </si>
   <si>
@@ -828,9 +704,6 @@
     <t>Dlx1as,Pgm1,Cntnap5c,Ackr3,Gria4,Dlgap1</t>
   </si>
   <si>
-    <t>Lhx6,Ostm1,Arx,Erbb4,Rai2,Slc6a1</t>
-  </si>
-  <si>
     <t>Lhx6,Smoc1,Sh3rf3,Sox6,Rai2,Dclk2</t>
   </si>
   <si>
@@ -840,12 +713,6 @@
     <t>Adarb2,Htr3a,Slain1,Erbb4,Bmper,Pdzrn3</t>
   </si>
   <si>
-    <t>Npas1,Gm2516,Nr3c2,Cnr1,Ubash3b,Npas3</t>
-  </si>
-  <si>
-    <t>Rasgrp1,D930028M14Rik,Onecut2,Aifm3,Zdbf2,Klhdc8b</t>
-  </si>
-  <si>
     <t>Samd3,Kif26a,Uncx,Nrp2,Ncam2,Ccser1</t>
   </si>
   <si>
@@ -888,15 +755,6 @@
     <t>Nts,Gm28175,Tfap2e,Sorcs3,Nebl,Brca1</t>
   </si>
   <si>
-    <t>Calb2,Fgf15,Zic4,Chst1,Rab3b,Ncald</t>
-  </si>
-  <si>
-    <t>Fam19a1,Igfbp7,Cbln2,Adamts19,Ankfn1,Ncald</t>
-  </si>
-  <si>
-    <t>Tesc,Hdac11,Camk2n1,Adamts19,March1,Ncald</t>
-  </si>
-  <si>
     <t>Pmch,Cntnap5b,Fam46a,Dmrtb1,Lrrtm4,Wdpcp</t>
   </si>
   <si>
@@ -924,54 +782,6 @@
     <t>Samd3,Ak5,Fam189a1,Gm21949,Fgf12,Nrg3</t>
   </si>
   <si>
-    <t>Thrsp,Pdlim3,Hopx,Adamts19,Emid1,Rgs20</t>
-  </si>
-  <si>
-    <t>Dorsal forebrain</t>
-  </si>
-  <si>
-    <t>RglDF2</t>
-  </si>
-  <si>
-    <t>E330013P04Rik,Gmpr,Htra1,Loxl1,Mt2,Tnfrsf19</t>
-  </si>
-  <si>
-    <t>Ccdc80,Usp50,Ltbp1,Loxl1,Celsr1,Samd4</t>
-  </si>
-  <si>
-    <t>E330013P04Rik,Kif24,Ltbp1,Cav1,Hes1,Csmd1</t>
-  </si>
-  <si>
-    <t>Gm29260,Gm26604,G630016G05Rik,Jph1,Thsd4,Rgs20</t>
-  </si>
-  <si>
-    <t>Dct,2810459M11Rik,Cdon,Mir670hg,Ndrg2,Rgs20</t>
-  </si>
-  <si>
-    <t>Gm29260,Gnb2,Etl4,Jph1,Hes1,Rgs20</t>
-  </si>
-  <si>
-    <t>Gm29260,Pknox1,Etl4,Jph1,Plce1,Rgs20</t>
-  </si>
-  <si>
-    <t>Nr2e1,A630089N07Rik,Katnal2,Jph1,Gli3,Efnb1</t>
-  </si>
-  <si>
-    <t>Dmrt3,Dsn1,Dmrta2,Gas1,Sfrp1,Psrc1</t>
-  </si>
-  <si>
-    <t>Dmrt3,Ncapg2,Dmrta2,Lrrn1,Gli3,Ung</t>
-  </si>
-  <si>
-    <t>Dmrt3,Hist1h2an,Rbm20,Jph1,Hist1h1b,Fut9</t>
-  </si>
-  <si>
-    <t>Dmrt3,Msrb3,Dmrta2,Gas1,Plagl1,Tnfrsf19</t>
-  </si>
-  <si>
-    <t>E330013P04Rik,Dmrt1,Rhcg,Lrrn1,Tmem132c,Flrt3</t>
-  </si>
-  <si>
     <t>Nr2e1,Slc12a7,Hmga2,Wnt5b,Mecom,Filip1</t>
   </si>
   <si>
@@ -981,27 +791,9 @@
     <t>Emx2,Zfp992,Dmrta2,Gpc4,Gli3,Efnb1</t>
   </si>
   <si>
-    <t>RglF8</t>
-  </si>
-  <si>
-    <t>Fgf17,Mir9-3hg,Spry1,Gm29266,Rmst,Shroom3</t>
-  </si>
-  <si>
-    <t>RglF10</t>
-  </si>
-  <si>
-    <t>Fgf17,C130060K24Rik,Spry1,Nr6a1os,Gbe1,Dusp6</t>
-  </si>
-  <si>
     <t>Nr2e1,Lama1,Ptx3,Fgfr3,Nrarp,Sema5b</t>
   </si>
   <si>
-    <t>RglF13</t>
-  </si>
-  <si>
-    <t>Gsx2,Wdr36,Rgcc,Adgrv1,Napepld,Sema5b</t>
-  </si>
-  <si>
     <t>GABA_F1</t>
   </si>
   <si>
@@ -1020,48 +812,27 @@
     <t>GABA_F6</t>
   </si>
   <si>
-    <t>GABA_F7</t>
-  </si>
-  <si>
     <t>GABA_F8</t>
   </si>
   <si>
     <t>GABA_F9</t>
   </si>
   <si>
-    <t>GABA_F10</t>
-  </si>
-  <si>
-    <t>GABA_F11</t>
-  </si>
-  <si>
     <t>GABA_F12</t>
   </si>
   <si>
-    <t>GABA_F13</t>
-  </si>
-  <si>
     <t>GABA_F14</t>
   </si>
   <si>
     <t>GABA_F15</t>
   </si>
   <si>
-    <t>GABA_F16</t>
-  </si>
-  <si>
     <t>GABA_F17</t>
   </si>
   <si>
-    <t>GABA_F18</t>
-  </si>
-  <si>
     <t>GABA_F19</t>
   </si>
   <si>
-    <t>GABA_F20</t>
-  </si>
-  <si>
     <t>GABA_F21</t>
   </si>
   <si>
@@ -1074,9 +845,6 @@
     <t>GABA_F25</t>
   </si>
   <si>
-    <t>GABA_F26</t>
-  </si>
-  <si>
     <t>GABA_F27</t>
   </si>
   <si>
@@ -1104,9 +872,6 @@
     <t>GABA_F35</t>
   </si>
   <si>
-    <t>GABA_F36</t>
-  </si>
-  <si>
     <t>GABA_F37</t>
   </si>
   <si>
@@ -1137,9 +902,6 @@
     <t>GABA_F47</t>
   </si>
   <si>
-    <t>GABA_F48</t>
-  </si>
-  <si>
     <t>GABA_F49</t>
   </si>
   <si>
@@ -1149,9 +911,6 @@
     <t>GABA_F51</t>
   </si>
   <si>
-    <t>GABA_F52</t>
-  </si>
-  <si>
     <t>GABA_F53</t>
   </si>
   <si>
@@ -1161,9 +920,6 @@
     <t>GABA_F56</t>
   </si>
   <si>
-    <t>GABA_F57</t>
-  </si>
-  <si>
     <t>GABA_F58</t>
   </si>
   <si>
@@ -1197,9 +953,6 @@
     <t>Glut_F10</t>
   </si>
   <si>
-    <t>Glut_F11</t>
-  </si>
-  <si>
     <t>Glut_F12</t>
   </si>
   <si>
@@ -1230,15 +983,6 @@
     <t>Glut_F27</t>
   </si>
   <si>
-    <t>Glut_F32</t>
-  </si>
-  <si>
-    <t>Glut_F33</t>
-  </si>
-  <si>
-    <t>Glut_F34</t>
-  </si>
-  <si>
     <t>Glut_F39</t>
   </si>
   <si>
@@ -1257,15 +1001,9 @@
     <t>Epen_F1</t>
   </si>
   <si>
-    <t>Astro_F1</t>
-  </si>
-  <si>
     <t>Gliob_F1</t>
   </si>
   <si>
-    <t>Gliob_F3</t>
-  </si>
-  <si>
     <t>Gliob_F4</t>
   </si>
   <si>
@@ -1287,51 +1025,6 @@
     <t>Gliob_F10</t>
   </si>
   <si>
-    <t>RGC_DF1</t>
-  </si>
-  <si>
-    <t>RGC_DF2</t>
-  </si>
-  <si>
-    <t>RGC_DF3</t>
-  </si>
-  <si>
-    <t>RGC_DF4</t>
-  </si>
-  <si>
-    <t>RGC_DF5</t>
-  </si>
-  <si>
-    <t>RGC_DF6</t>
-  </si>
-  <si>
-    <t>RGC_DF7</t>
-  </si>
-  <si>
-    <t>RGC_DF8</t>
-  </si>
-  <si>
-    <t>RGC_DF10</t>
-  </si>
-  <si>
-    <t>RGC_DF11</t>
-  </si>
-  <si>
-    <t>RGC_DF12</t>
-  </si>
-  <si>
-    <t>RGC_DF13</t>
-  </si>
-  <si>
-    <t>RGC_DF14</t>
-  </si>
-  <si>
-    <t>RGC_DF15</t>
-  </si>
-  <si>
-    <t>Nbl_F1</t>
-  </si>
-  <si>
     <t>Nbl_F3</t>
   </si>
   <si>
@@ -1341,9 +1034,6 @@
     <t>RGC_F1</t>
   </si>
   <si>
-    <t>RGC_F2</t>
-  </si>
-  <si>
     <t>RGC_F3</t>
   </si>
   <si>
@@ -1356,30 +1046,18 @@
     <t>RGC_F6</t>
   </si>
   <si>
-    <t>RGC_F7</t>
-  </si>
-  <si>
-    <t>RGC_F9</t>
-  </si>
-  <si>
     <t>RGC_F10</t>
   </si>
   <si>
     <t>RGC_F11</t>
   </si>
   <si>
-    <t>RGC_F12</t>
-  </si>
-  <si>
     <t>RGC_F13</t>
   </si>
   <si>
     <t>Radial glial cells</t>
   </si>
   <si>
-    <t>Vim,Pax6,Tnc,Fabp7,Hes1,Sox2,Hes5,Nes,Ptprz1</t>
-  </si>
-  <si>
     <t>Cortex</t>
   </si>
   <si>
@@ -1515,12 +1193,6 @@
     <t>Fibroblasts</t>
   </si>
   <si>
-    <t>Col1a1,Col1a2,Col5a1,Col3a1,Col6a3</t>
-  </si>
-  <si>
-    <t>Muhl et al.,Nat Comm 2020;PMID: 33560373</t>
-  </si>
-  <si>
     <t>Endothelial cells</t>
   </si>
   <si>
@@ -1725,9 +1397,6 @@
     <t>GABA_F15c</t>
   </si>
   <si>
-    <t>Wrong annotation</t>
-  </si>
-  <si>
     <t>Glut_F16c</t>
   </si>
   <si>
@@ -1749,36 +1418,6 @@
     <t>Astro1</t>
   </si>
   <si>
-    <t>Gpc5,Slc1a2,Slc1a3,Apoe,Wdr17,Plpp3,Rorb,Rmst,Slc4a4,Htra1</t>
-  </si>
-  <si>
-    <t>Motor Cortex</t>
-  </si>
-  <si>
-    <t>Astro2</t>
-  </si>
-  <si>
-    <t>Gpc5,Myoc,Slc1a2,Fxyd6,Slc1a3,Nrp2,Slc6a6,Apoe,Aqp4,Gfap</t>
-  </si>
-  <si>
-    <t>Lsamp,Gpc5,Slc1a2,Luzp2,Slc1a3,Apoe,Cadm2,Rora,Aqp4,Slc7a10</t>
-  </si>
-  <si>
-    <t>Igfbpl1,Gpc5,Mki67,Slc1a2,Myt1,Slc1a3,Apoe,E2f2,E2f7,Top2a</t>
-  </si>
-  <si>
-    <t>Astro3</t>
-  </si>
-  <si>
-    <t>Astro4</t>
-  </si>
-  <si>
-    <t>Astro5</t>
-  </si>
-  <si>
-    <t>PMID: 34616066</t>
-  </si>
-  <si>
     <t>nIPC2</t>
   </si>
   <si>
@@ -1791,15 +1430,6 @@
     <t>GABA_F19c</t>
   </si>
   <si>
-    <t>Wrong annotation?</t>
-  </si>
-  <si>
-    <t>Pla2g7,Timp4,Slc6a11,Egfr</t>
-  </si>
-  <si>
-    <t>Astro6</t>
-  </si>
-  <si>
     <t>Epen2</t>
   </si>
   <si>
@@ -1815,354 +1445,6 @@
     <t>Glut_F22c</t>
   </si>
   <si>
-    <t>PMID: 38092916</t>
-  </si>
-  <si>
-    <t>3 HY-EA-Glut-GABA</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut</t>
-  </si>
-  <si>
-    <t>Samd3,Fezf2,Car10,Ccn3</t>
-  </si>
-  <si>
-    <t>119 SI-MA-LPO-LHA Skor1 Glut</t>
-  </si>
-  <si>
-    <t>Dmrta2,Piezo2,Sntg2</t>
-  </si>
-  <si>
-    <t>Samd3,Skor1,Six3,Megf11</t>
-  </si>
-  <si>
-    <t>Il31ra,Galr1,G630016G05Rik,Dmrta2</t>
-  </si>
-  <si>
-    <t>Dmrta2,Cnga3,Zeb2</t>
-  </si>
-  <si>
-    <t>Samd3,Cxcl12,Tmem132c,Cck,Galntl6</t>
-  </si>
-  <si>
-    <t>Dmrta2,Egflam,Tcf7l2</t>
-  </si>
-  <si>
-    <t>Tgfbi,Cnga3,Lama1</t>
-  </si>
-  <si>
-    <t>Astro-CB NN_1</t>
-  </si>
-  <si>
-    <t>Dao,Cyp26b1,Emid1</t>
-  </si>
-  <si>
-    <t>Astro-Epen</t>
-  </si>
-  <si>
-    <t>317 Astro-CB NN</t>
-  </si>
-  <si>
-    <t>7 NN-IMN-GC</t>
-  </si>
-  <si>
-    <t>Astro-NT NN_1</t>
-  </si>
-  <si>
-    <t>Gfap,Lhfpl3,Gria1,Hopx</t>
-  </si>
-  <si>
-    <t>318 Astro-NT NN</t>
-  </si>
-  <si>
-    <t>Astro-NT NN_2</t>
-  </si>
-  <si>
-    <t>Gja1,A330076C08Rik,Itih3,Gria2</t>
-  </si>
-  <si>
-    <t>Astro-TE NN_1</t>
-  </si>
-  <si>
-    <t>Myoc,Camk2a</t>
-  </si>
-  <si>
-    <t>319 Astro-TE NN</t>
-  </si>
-  <si>
-    <t>Astro-TE NN_2</t>
-  </si>
-  <si>
-    <t>Hepacam,E330013P04Rik</t>
-  </si>
-  <si>
-    <t>Astro-TE NN_3</t>
-  </si>
-  <si>
-    <t>Gja1,Grin2c,Dcc,Slc7a10</t>
-  </si>
-  <si>
-    <t>Astro-TE NN_4</t>
-  </si>
-  <si>
-    <t>Gfap,Thbs4,Gm29683</t>
-  </si>
-  <si>
-    <t>Astro-TE NN_5</t>
-  </si>
-  <si>
-    <t>Gja1,Thbs4,Kcnk10,Pak1</t>
-  </si>
-  <si>
-    <t>Astro-OLF NN_1</t>
-  </si>
-  <si>
-    <t>Aqp4,Prss23,Igfbp2</t>
-  </si>
-  <si>
-    <t>320 Astro-OLF NN</t>
-  </si>
-  <si>
-    <t>Astro-OLF NN_2</t>
-  </si>
-  <si>
-    <t>Gja1,Hs3st3a1,Slco1c1</t>
-  </si>
-  <si>
-    <t>Astro-OLF NN_3</t>
-  </si>
-  <si>
-    <t>Ednrb,Hs3st3a1,C230072F16Rik,Gria2</t>
-  </si>
-  <si>
-    <t>Astroependymal NN_1</t>
-  </si>
-  <si>
-    <t>Gfap,Cnmd,Id1,Fabp7</t>
-  </si>
-  <si>
-    <t>321 Astroependymal NN</t>
-  </si>
-  <si>
-    <t>Astroependymal NN_2</t>
-  </si>
-  <si>
-    <t>Wt1</t>
-  </si>
-  <si>
-    <t>Astroependymal NN_3</t>
-  </si>
-  <si>
-    <t>Gfap,Prokr2,Itih3</t>
-  </si>
-  <si>
-    <t>Tanycyte NN_1</t>
-  </si>
-  <si>
-    <t>Cnmd,Lpl</t>
-  </si>
-  <si>
-    <t>322 Tanycyte NN</t>
-  </si>
-  <si>
-    <t>Tanycyte NN_2</t>
-  </si>
-  <si>
-    <t>Gpr50,Ccdc170,Nkx2-4</t>
-  </si>
-  <si>
-    <t>Tanycyte NN_3</t>
-  </si>
-  <si>
-    <t>Fndc3c1</t>
-  </si>
-  <si>
-    <t>Ependymal NN_1</t>
-  </si>
-  <si>
-    <t>Ccdc153,Dnah3</t>
-  </si>
-  <si>
-    <t>323 Ependymal NN</t>
-  </si>
-  <si>
-    <t>Ependymal NN_2</t>
-  </si>
-  <si>
-    <t>Tmem212,Rarres2</t>
-  </si>
-  <si>
-    <t>Hypendymal NN_1</t>
-  </si>
-  <si>
-    <t>Sspo,Spag17</t>
-  </si>
-  <si>
-    <t>324 Hypendymal NN</t>
-  </si>
-  <si>
-    <t>CHOR NN_1</t>
-  </si>
-  <si>
-    <t>2900040C04Rik</t>
-  </si>
-  <si>
-    <t>325 CHOR NN</t>
-  </si>
-  <si>
-    <t>OPC NN_1</t>
-  </si>
-  <si>
-    <t>Pdgfra,Olig1,Rmi2</t>
-  </si>
-  <si>
-    <t>OPC-Oligo</t>
-  </si>
-  <si>
-    <t>326 OPC NN</t>
-  </si>
-  <si>
-    <t>OPC NN_2</t>
-  </si>
-  <si>
-    <t>Cenpf,Pdgfra</t>
-  </si>
-  <si>
-    <t>VLMC NN_1</t>
-  </si>
-  <si>
-    <t>Igf2,Slc13a3</t>
-  </si>
-  <si>
-    <t>330 VLMC NN</t>
-  </si>
-  <si>
-    <t>VLMC NN_2</t>
-  </si>
-  <si>
-    <t>Apod,Slc6a13,Col15a1</t>
-  </si>
-  <si>
-    <t>VLMC NN_3</t>
-  </si>
-  <si>
-    <t>Alpl,Moxd1</t>
-  </si>
-  <si>
-    <t>VLMC NN_4</t>
-  </si>
-  <si>
-    <t>Apod,Tfap2b,Il33</t>
-  </si>
-  <si>
-    <t>Peri NN_1</t>
-  </si>
-  <si>
-    <t>Vtn,Abcc9</t>
-  </si>
-  <si>
-    <t>331 Peri NN</t>
-  </si>
-  <si>
-    <t>SMC NN_1</t>
-  </si>
-  <si>
-    <t>Acta2,Myh11</t>
-  </si>
-  <si>
-    <t>332 SMC NN</t>
-  </si>
-  <si>
-    <t>Endo NN_1</t>
-  </si>
-  <si>
-    <t>Ly6c1</t>
-  </si>
-  <si>
-    <t>333 Endo NN</t>
-  </si>
-  <si>
-    <t>Microglia NN_1</t>
-  </si>
-  <si>
-    <t>C1qa,Tmem119</t>
-  </si>
-  <si>
-    <t>334 Microglia NN</t>
-  </si>
-  <si>
-    <t>Monocytes NN_1</t>
-  </si>
-  <si>
-    <t>Il1b,S100a9</t>
-  </si>
-  <si>
-    <t>336 Monocytes NN</t>
-  </si>
-  <si>
-    <t>DC NN_1</t>
-  </si>
-  <si>
-    <t>Cd74,Lyz2</t>
-  </si>
-  <si>
-    <t>337 DC NN</t>
-  </si>
-  <si>
-    <t>B cells NN_1</t>
-  </si>
-  <si>
-    <t>Cd74,Igkc</t>
-  </si>
-  <si>
-    <t>338 Lymphoid NN</t>
-  </si>
-  <si>
-    <t>ILC NN_2</t>
-  </si>
-  <si>
-    <t>Il1rl1,Gata3</t>
-  </si>
-  <si>
-    <t>NK cells NN_3</t>
-  </si>
-  <si>
-    <t>Ccl5,Fcer1g</t>
-  </si>
-  <si>
-    <t>T cells NN_4</t>
-  </si>
-  <si>
-    <t>Itk,Cd3d</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut1</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut2</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut3</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut4</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut5</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut6</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut7</t>
-  </si>
-  <si>
-    <t>CNU-HYa Glut8</t>
-  </si>
-  <si>
-    <t>Btg2</t>
-  </si>
-  <si>
     <t>Cell cycling</t>
   </si>
   <si>
@@ -2187,9 +1469,6 @@
     <t>Microglia1</t>
   </si>
   <si>
-    <t>GABA_F6c</t>
-  </si>
-  <si>
     <t>Isl1,Pkib,Cdh7,Cdkn1c,Syt1</t>
   </si>
   <si>
@@ -2212,9 +1491,6 @@
   </si>
   <si>
     <t>Pcdh11x,Tox2,Slit2,Mbip,Shc3</t>
-  </si>
-  <si>
-    <t>Lpl,Ano1,Ccnd1,Mbip,Mest</t>
   </si>
   <si>
     <t>Gm29508,Dach2,Ptch1,Crb2,Sox2</t>
@@ -2239,7 +1515,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2274,38 +1550,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2330,7 +1581,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2338,11 +1589,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2702,19 +1949,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>446</v>
+        <v>340</v>
       </c>
       <c r="C2" t="s">
-        <v>722</v>
+        <v>482</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K2" t="s">
-        <v>449</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2722,10 +1969,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>450</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>451</v>
+        <v>344</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -2734,10 +1981,10 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K3" t="s">
-        <v>452</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2745,22 +1992,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="C4" t="s">
-        <v>454</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
         <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="I4" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>456</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2768,22 +2015,22 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>457</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>723</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="I5" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K5" t="s">
-        <v>458</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2791,22 +2038,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>459</v>
+        <v>352</v>
       </c>
       <c r="C6" t="s">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>455</v>
+        <v>348</v>
       </c>
       <c r="I6" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>460</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -2814,22 +2061,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>710</v>
+        <v>471</v>
       </c>
       <c r="E7" t="s">
-        <v>461</v>
+        <v>354</v>
       </c>
       <c r="G7" t="s">
-        <v>709</v>
+        <v>470</v>
       </c>
       <c r="I7" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K7" t="s">
-        <v>462</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2837,22 +2084,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>463</v>
+        <v>356</v>
       </c>
       <c r="C8" t="s">
-        <v>719</v>
+        <v>479</v>
       </c>
       <c r="E8" t="s">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="G8" t="s">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="I8" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K8" t="s">
-        <v>465</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2860,22 +2107,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>466</v>
+        <v>359</v>
       </c>
       <c r="C9" t="s">
-        <v>467</v>
+        <v>360</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G9" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I9" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K9" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2883,22 +2130,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>363</v>
       </c>
       <c r="C10" t="s">
-        <v>471</v>
+        <v>364</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G10" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I10" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>472</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -2906,22 +2153,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>473</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>474</v>
+        <v>367</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G11" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I11" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K11" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -2929,22 +2176,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>475</v>
+        <v>368</v>
       </c>
       <c r="C12" t="s">
-        <v>476</v>
+        <v>369</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G12" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I12" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K12" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -2952,22 +2199,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>477</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
-        <v>478</v>
+        <v>371</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G13" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I13" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>472</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -2975,22 +2222,22 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>479</v>
+        <v>372</v>
       </c>
       <c r="C14" t="s">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G14" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I14" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K14" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2998,22 +2245,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>481</v>
+        <v>374</v>
       </c>
       <c r="C15" t="s">
-        <v>482</v>
+        <v>375</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I15" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K15" t="s">
-        <v>469</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -3021,22 +2268,22 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>483</v>
+        <v>376</v>
       </c>
       <c r="C16" t="s">
-        <v>484</v>
+        <v>377</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G16" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="I16" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K16" t="s">
-        <v>485</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -3044,25 +2291,25 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>553</v>
+        <v>444</v>
       </c>
       <c r="C17" t="s">
-        <v>721</v>
+        <v>481</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="H17" t="s">
-        <v>552</v>
+        <v>443</v>
       </c>
       <c r="I17" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>486</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -3070,19 +2317,19 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>487</v>
+        <v>380</v>
       </c>
       <c r="C18" t="s">
-        <v>523</v>
+        <v>414</v>
       </c>
       <c r="E18" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="I18" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>488</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -3090,19 +2337,19 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>489</v>
+        <v>382</v>
       </c>
       <c r="C19" t="s">
-        <v>490</v>
+        <v>383</v>
       </c>
       <c r="E19" t="s">
+        <v>384</v>
+      </c>
+      <c r="I19" t="s">
+        <v>341</v>
+      </c>
+      <c r="K19" t="s">
         <v>491</v>
-      </c>
-      <c r="I19" t="s">
-        <v>448</v>
-      </c>
-      <c r="K19" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -3110,19 +2357,19 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>492</v>
+        <v>385</v>
       </c>
       <c r="C20" t="s">
-        <v>724</v>
+        <v>484</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I20" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>731</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -3130,19 +2377,19 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>495</v>
+        <v>386</v>
       </c>
       <c r="C21" t="s">
-        <v>496</v>
+        <v>387</v>
       </c>
       <c r="E21" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
-        <v>497</v>
+        <v>388</v>
       </c>
       <c r="K21" t="s">
-        <v>498</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -3150,19 +2397,19 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>499</v>
+        <v>390</v>
       </c>
       <c r="C22" t="s">
-        <v>500</v>
+        <v>391</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>501</v>
+        <v>392</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -3170,16 +2417,16 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>503</v>
+        <v>394</v>
       </c>
       <c r="C23" t="s">
-        <v>504</v>
+        <v>395</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G23" t="s">
-        <v>501</v>
+        <v>392</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -3188,16 +2435,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>505</v>
+        <v>396</v>
       </c>
       <c r="C24" t="s">
-        <v>506</v>
+        <v>397</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G24" t="s">
-        <v>501</v>
+        <v>392</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -3206,16 +2453,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>507</v>
+        <v>398</v>
       </c>
       <c r="C25" t="s">
-        <v>508</v>
+        <v>399</v>
       </c>
       <c r="E25" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -3223,16 +2470,16 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>509</v>
+        <v>400</v>
       </c>
       <c r="C26" t="s">
-        <v>510</v>
+        <v>401</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -3240,16 +2487,16 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>511</v>
+        <v>402</v>
       </c>
       <c r="C27" t="s">
-        <v>512</v>
+        <v>403</v>
       </c>
       <c r="E27" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -3257,19 +2504,19 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="C28" t="s">
-        <v>514</v>
+        <v>405</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G28" t="s">
-        <v>515</v>
+        <v>406</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -3277,19 +2524,19 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>516</v>
+        <v>407</v>
       </c>
       <c r="C29" t="s">
-        <v>517</v>
+        <v>408</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G29" t="s">
-        <v>515</v>
+        <v>406</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -3297,16 +2544,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>518</v>
+        <v>409</v>
       </c>
       <c r="C30" t="s">
-        <v>519</v>
+        <v>410</v>
       </c>
       <c r="E30" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>502</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3314,16 +2561,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>520</v>
+        <v>411</v>
       </c>
       <c r="C31" t="s">
-        <v>521</v>
+        <v>412</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>522</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -3580,19 +2827,19 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G44" t="s">
         <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K44" t="s">
         <v>17</v>
@@ -3603,10 +2850,10 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -3615,7 +2862,7 @@
         <v>38</v>
       </c>
       <c r="H45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K45" t="s">
         <v>17</v>
@@ -3626,19 +2873,19 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G46" t="s">
         <v>38</v>
       </c>
       <c r="H46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K46" t="s">
         <v>17</v>
@@ -3649,19 +2896,19 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G47" t="s">
         <v>38</v>
       </c>
       <c r="H47" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K47" t="s">
         <v>17</v>
@@ -3672,19 +2919,19 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G48" t="s">
         <v>38</v>
       </c>
       <c r="H48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K48" t="s">
         <v>17</v>
@@ -3695,19 +2942,19 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G49" t="s">
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K49" t="s">
         <v>17</v>
@@ -3718,19 +2965,19 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G50" t="s">
         <v>38</v>
       </c>
       <c r="H50" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K50" t="s">
         <v>17</v>
@@ -3741,19 +2988,19 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G51" t="s">
         <v>38</v>
       </c>
       <c r="H51" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K51" t="s">
         <v>17</v>
@@ -3764,19 +3011,19 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G52" t="s">
         <v>38</v>
       </c>
       <c r="H52" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K52" t="s">
         <v>17</v>
@@ -3787,19 +3034,19 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G53" t="s">
         <v>38</v>
       </c>
       <c r="H53" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K53" t="s">
         <v>17</v>
@@ -3810,19 +3057,19 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G54" t="s">
         <v>38</v>
       </c>
       <c r="H54" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K54" t="s">
         <v>17</v>
@@ -3833,10 +3080,10 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
@@ -3856,10 +3103,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
         <v>38</v>
@@ -3879,10 +3126,10 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
         <v>38</v>
@@ -3902,10 +3149,10 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E58" t="s">
         <v>38</v>
@@ -3914,7 +3161,7 @@
         <v>38</v>
       </c>
       <c r="H58" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K58" t="s">
         <v>17</v>
@@ -3925,10 +3172,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E59" t="s">
         <v>38</v>
@@ -3937,7 +3184,7 @@
         <v>38</v>
       </c>
       <c r="H59" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K59" t="s">
         <v>17</v>
@@ -3948,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E60" t="s">
         <v>38</v>
@@ -3960,7 +3207,7 @@
         <v>38</v>
       </c>
       <c r="H60" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K60" t="s">
         <v>17</v>
@@ -3971,16 +3218,16 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -3994,16 +3241,16 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -4017,19 +3264,19 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E63" t="s">
+        <v>73</v>
+      </c>
+      <c r="G63" t="s">
+        <v>73</v>
+      </c>
+      <c r="H63" t="s">
         <v>76</v>
-      </c>
-      <c r="G63" t="s">
-        <v>76</v>
-      </c>
-      <c r="H63" t="s">
-        <v>81</v>
       </c>
       <c r="K63" t="s">
         <v>17</v>
@@ -4040,19 +3287,19 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E64" t="s">
+        <v>73</v>
+      </c>
+      <c r="G64" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" t="s">
         <v>76</v>
-      </c>
-      <c r="G64" t="s">
-        <v>76</v>
-      </c>
-      <c r="H64" t="s">
-        <v>81</v>
       </c>
       <c r="K64" t="s">
         <v>17</v>
@@ -4063,19 +3310,19 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C65" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E65" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" t="s">
+        <v>73</v>
+      </c>
+      <c r="H65" t="s">
         <v>76</v>
-      </c>
-      <c r="G65" t="s">
-        <v>76</v>
-      </c>
-      <c r="H65" t="s">
-        <v>81</v>
       </c>
       <c r="K65" t="s">
         <v>17</v>
@@ -4086,16 +3333,16 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -4109,16 +3356,16 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -4132,19 +3379,19 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H68" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
@@ -4155,19 +3402,19 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="K69" t="s">
         <v>17</v>
@@ -4178,19 +3425,19 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="K70" t="s">
         <v>17</v>
@@ -4201,19 +3448,19 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="K71" t="s">
         <v>17</v>
@@ -4224,19 +3471,19 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="K72" t="s">
         <v>17</v>
@@ -4247,19 +3494,19 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E73" t="s">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s">
         <v>104</v>
-      </c>
-      <c r="G73" t="s">
-        <v>104</v>
-      </c>
-      <c r="H73" t="s">
-        <v>127</v>
       </c>
       <c r="K73" t="s">
         <v>17</v>
@@ -4270,19 +3517,19 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="K74" t="s">
         <v>17</v>
@@ -4293,19 +3540,19 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C75" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="K75" t="s">
         <v>17</v>
@@ -4316,19 +3563,19 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C76" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="E76" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="K76" t="s">
         <v>17</v>
@@ -4339,19 +3586,19 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>716</v>
+        <v>477</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H77" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="K77" t="s">
         <v>17</v>
@@ -4362,19 +3609,19 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>715</v>
+        <v>476</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="E78" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H78" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="K78" t="s">
         <v>17</v>
@@ -4385,19 +3632,19 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>714</v>
+        <v>475</v>
       </c>
       <c r="C79" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H79" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="K79" t="s">
         <v>17</v>
@@ -4408,19 +3655,19 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>712</v>
+        <v>473</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E80" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G80" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H80" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="K80" t="s">
         <v>17</v>
@@ -4431,19 +3678,19 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>711</v>
+        <v>472</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="E81" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G81" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H81" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="K81" t="s">
         <v>17</v>
@@ -4454,19 +3701,19 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>713</v>
+        <v>474</v>
       </c>
       <c r="C82" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="E82" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G82" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H82" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="K82" t="s">
         <v>17</v>
@@ -4477,19 +3724,19 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E83" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G83" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H83" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K83" t="s">
         <v>17</v>
@@ -4500,19 +3747,19 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C84" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="E84" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G84" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H84" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K84" t="s">
         <v>17</v>
@@ -4523,19 +3770,19 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G85" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H85" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K85" t="s">
         <v>17</v>
@@ -4546,19 +3793,19 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C86" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="E86" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G86" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H86" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
@@ -4569,19 +3816,19 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="C87" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="E87" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G87" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H87" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K87" t="s">
         <v>17</v>
@@ -4592,19 +3839,19 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C88" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E88" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="G88" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="H88" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K88" t="s">
         <v>17</v>
@@ -4615,19 +3862,19 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="C89" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="G89" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I89" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K89" t="s">
         <v>17</v>
@@ -4638,19 +3885,19 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>408</v>
+        <v>322</v>
       </c>
       <c r="C90" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E90" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G90" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I90" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K90" t="s">
         <v>17</v>
@@ -4661,19 +3908,19 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>416</v>
+        <v>329</v>
       </c>
       <c r="C91" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E91" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G91" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I91" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
@@ -4684,19 +3931,19 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>410</v>
+        <v>323</v>
       </c>
       <c r="C92" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="E92" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G92" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I92" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K92" t="s">
         <v>17</v>
@@ -4707,19 +3954,19 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="C93" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G93" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I93" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K93" t="s">
         <v>17</v>
@@ -4730,19 +3977,19 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="C94" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E94" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G94" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I94" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K94" t="s">
         <v>17</v>
@@ -4753,19 +4000,19 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>413</v>
+        <v>326</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="E95" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G95" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I95" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K95" t="s">
         <v>17</v>
@@ -4776,19 +4023,19 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="C96" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="E96" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G96" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I96" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K96" t="s">
         <v>17</v>
@@ -4799,19 +4046,19 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="C97" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="E97" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G97" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I97" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K97" t="s">
         <v>17</v>
@@ -4822,19 +4069,19 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="C98" t="s">
-        <v>728</v>
+        <v>487</v>
       </c>
       <c r="E98" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G98" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I98" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K98" t="s">
         <v>17</v>
@@ -4845,19 +4092,19 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>442</v>
+        <v>337</v>
       </c>
       <c r="C99" t="s">
-        <v>725</v>
+        <v>485</v>
       </c>
       <c r="E99" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G99" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I99" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K99" t="s">
         <v>17</v>
@@ -4868,19 +4115,19 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>443</v>
+        <v>338</v>
       </c>
       <c r="C100" t="s">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="E100" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G100" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I100" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K100" t="s">
         <v>17</v>
@@ -4891,19 +4138,19 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>445</v>
+        <v>339</v>
       </c>
       <c r="C101" t="s">
-        <v>729</v>
+        <v>488</v>
       </c>
       <c r="E101" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G101" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I101" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K101" t="s">
         <v>17</v>
@@ -4914,19 +4161,19 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>436</v>
+        <v>333</v>
       </c>
       <c r="C102" t="s">
-        <v>727</v>
+        <v>486</v>
       </c>
       <c r="E102" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G102" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I102" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K102" t="s">
         <v>17</v>
@@ -4937,19 +4184,19 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="C103" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G103" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I103" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K103" t="s">
         <v>17</v>
@@ -4960,19 +4207,19 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="C104" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="E104" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G104" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I104" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K104" t="s">
         <v>17</v>
@@ -4983,19 +4230,19 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>439</v>
+        <v>336</v>
       </c>
       <c r="C105" t="s">
-        <v>314</v>
+        <v>251</v>
       </c>
       <c r="E105" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="G105" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I105" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K105" t="s">
         <v>17</v>
@@ -5006,19 +4253,19 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>432</v>
+        <v>330</v>
       </c>
       <c r="C106" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="G106" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="I106" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K106" t="s">
         <v>17</v>
@@ -5029,19 +4276,19 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>433</v>
+        <v>331</v>
       </c>
       <c r="C107" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E107" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="G107" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="I107" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="K107" t="s">
         <v>17</v>
@@ -5052,19 +4299,19 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="E108" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G108" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I108" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K108" t="s">
         <v>17</v>
@@ -5075,19 +4322,19 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="C109" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="E109" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G109" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I109" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K109" t="s">
         <v>17</v>
@@ -5098,19 +4345,19 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>335</v>
+        <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="E110" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G110" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I110" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K110" t="s">
         <v>17</v>
@@ -5121,19 +4368,19 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>336</v>
+        <v>263</v>
       </c>
       <c r="C111" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="E111" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G111" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I111" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K111" t="s">
         <v>17</v>
@@ -5144,19 +4391,19 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>338</v>
+        <v>264</v>
       </c>
       <c r="C112" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="E112" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G112" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I112" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K112" t="s">
         <v>17</v>
@@ -5167,19 +4414,19 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>564</v>
+        <v>454</v>
       </c>
       <c r="C113" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="E113" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G113" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I113" t="s">
-        <v>565</v>
+        <v>455</v>
       </c>
       <c r="K113" t="s">
         <v>17</v>
@@ -5190,19 +4437,19 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="C114" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="E114" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G114" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I114" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K114" t="s">
         <v>17</v>
@@ -5213,19 +4460,19 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="E115" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G115" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I115" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K115" t="s">
         <v>17</v>
@@ -5236,19 +4483,19 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="E116" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G116" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I116" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K116" t="s">
         <v>17</v>
@@ -5259,19 +4506,19 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>592</v>
+        <v>469</v>
       </c>
       <c r="C117" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="E117" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G117" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I117" t="s">
-        <v>565</v>
+        <v>455</v>
       </c>
       <c r="K117" t="s">
         <v>17</v>
@@ -5282,19 +4529,19 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="E118" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G118" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I118" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K118" t="s">
         <v>17</v>
@@ -5305,19 +4552,19 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="E119" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G119" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I119" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K119" t="s">
         <v>17</v>
@@ -5328,19 +4575,19 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="C120" t="s">
-        <v>730</v>
+        <v>489</v>
       </c>
       <c r="E120" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G120" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I120" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K120" t="s">
         <v>17</v>
@@ -5351,19 +4598,19 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C121" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="E121" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G121" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I121" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K121" t="s">
         <v>17</v>
@@ -5374,19 +4621,19 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="C122" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="E122" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G122" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I122" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K122" t="s">
         <v>17</v>
@@ -5397,19 +4644,19 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>349</v>
+        <v>272</v>
       </c>
       <c r="C123" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="E123" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G123" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I123" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K123" t="s">
         <v>17</v>
@@ -5420,19 +4667,19 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E124" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G124" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I124" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K124" t="s">
         <v>17</v>
@@ -5443,19 +4690,19 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>350</v>
+        <v>273</v>
       </c>
       <c r="C125" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="E125" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G125" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I125" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K125" t="s">
         <v>17</v>
@@ -5466,19 +4713,19 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>351</v>
+        <v>274</v>
       </c>
       <c r="C126" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="E126" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G126" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I126" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K126" t="s">
         <v>17</v>
@@ -5489,19 +4736,19 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C127" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="E127" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G127" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I127" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K127" t="s">
         <v>17</v>
@@ -5512,19 +4759,19 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="C128" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="E128" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G128" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I128" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K128" t="s">
         <v>17</v>
@@ -5535,19 +4782,19 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
       <c r="C129" t="s">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="E129" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G129" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I129" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K129" t="s">
         <v>17</v>
@@ -5558,19 +4805,19 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="C130" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="E130" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G130" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I130" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K130" t="s">
         <v>17</v>
@@ -5581,19 +4828,19 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>357</v>
+        <v>279</v>
       </c>
       <c r="C131" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="E131" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G131" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I131" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K131" t="s">
         <v>17</v>
@@ -5604,19 +4851,19 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>358</v>
+        <v>280</v>
       </c>
       <c r="C132" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="E132" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G132" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K132" t="s">
         <v>17</v>
@@ -5627,19 +4874,19 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>559</v>
+        <v>450</v>
       </c>
       <c r="C133" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="E133" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G133" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I133" t="s">
-        <v>556</v>
+        <v>447</v>
       </c>
       <c r="K133" t="s">
         <v>17</v>
@@ -5650,19 +4897,19 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="C134" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="E134" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G134" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I134" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K134" t="s">
         <v>17</v>
@@ -5673,19 +4920,19 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>359</v>
+        <v>281</v>
       </c>
       <c r="C135" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="E135" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G135" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I135" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K135" t="s">
         <v>17</v>
@@ -5696,19 +4943,19 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>360</v>
+        <v>282</v>
       </c>
       <c r="C136" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="E136" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G136" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I136" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K136" t="s">
         <v>17</v>
@@ -5719,19 +4966,19 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>361</v>
+        <v>283</v>
       </c>
       <c r="C137" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="E137" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G137" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I137" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K137" t="s">
         <v>17</v>
@@ -5742,19 +4989,19 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>362</v>
+        <v>284</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="E138" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G138" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I138" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K138" t="s">
         <v>17</v>
@@ -5765,19 +5012,19 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>363</v>
+        <v>285</v>
       </c>
       <c r="C139" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="E139" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G139" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I139" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K139" t="s">
         <v>17</v>
@@ -5788,19 +5035,19 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>364</v>
+        <v>286</v>
       </c>
       <c r="C140" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="E140" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G140" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I140" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K140" t="s">
         <v>17</v>
@@ -5811,19 +5058,19 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>365</v>
+        <v>287</v>
       </c>
       <c r="C141" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="E141" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G141" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I141" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K141" t="s">
         <v>17</v>
@@ -5834,19 +5081,19 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>366</v>
+        <v>288</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="E142" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G142" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I142" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K142" t="s">
         <v>17</v>
@@ -5857,19 +5104,19 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>368</v>
+        <v>289</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="E143" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G143" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I143" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K143" t="s">
         <v>17</v>
@@ -5880,19 +5127,19 @@
         <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>326</v>
+        <v>257</v>
       </c>
       <c r="C144" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="E144" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G144" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I144" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K144" t="s">
         <v>17</v>
@@ -5903,19 +5150,19 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>369</v>
+        <v>290</v>
       </c>
       <c r="C145" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="E145" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G145" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I145" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K145" t="s">
         <v>17</v>
@@ -5926,19 +5173,19 @@
         <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>370</v>
+        <v>291</v>
       </c>
       <c r="C146" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="E146" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G146" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I146" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K146" t="s">
         <v>17</v>
@@ -5949,19 +5196,19 @@
         <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>372</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="E147" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G147" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I147" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K147" t="s">
         <v>17</v>
@@ -5972,19 +5219,19 @@
         <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="E148" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G148" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I148" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K148" t="s">
         <v>17</v>
@@ -5995,19 +5242,19 @@
         <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="E149" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G149" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I149" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K149" t="s">
         <v>17</v>
@@ -6018,19 +5265,19 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
       <c r="C150" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="E150" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G150" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I150" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K150" t="s">
         <v>17</v>
@@ -6041,19 +5288,19 @@
         <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>377</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="E151" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G151" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I151" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K151" t="s">
         <v>17</v>
@@ -6064,19 +5311,19 @@
         <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="C152" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G152" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I152" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K152" t="s">
         <v>17</v>
@@ -6087,19 +5334,19 @@
         <v>11</v>
       </c>
       <c r="B153" t="s">
-        <v>378</v>
+        <v>297</v>
       </c>
       <c r="C153" t="s">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="E153" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G153" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I153" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K153" t="s">
         <v>17</v>
@@ -6110,19 +5357,19 @@
         <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>329</v>
+        <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E154" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G154" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I154" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K154" t="s">
         <v>17</v>
@@ -6133,19 +5380,19 @@
         <v>11</v>
       </c>
       <c r="B155" t="s">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="C155" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="E155" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G155" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I155" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="K155" t="s">
         <v>17</v>
@@ -6156,19 +5403,19 @@
         <v>11</v>
       </c>
       <c r="B156" t="s">
-        <v>379</v>
+        <v>298</v>
       </c>
       <c r="C156" t="s">
-        <v>718</v>
+        <v>478</v>
       </c>
       <c r="E156" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G156" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I156" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K156" t="s">
         <v>17</v>
@@ -6179,19 +5426,19 @@
         <v>11</v>
       </c>
       <c r="B157" t="s">
-        <v>386</v>
+        <v>305</v>
       </c>
       <c r="C157" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="E157" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G157" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I157" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K157" t="s">
         <v>17</v>
@@ -6202,19 +5449,19 @@
         <v>11</v>
       </c>
       <c r="B158" t="s">
-        <v>388</v>
+        <v>306</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="E158" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G158" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I158" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K158" t="s">
         <v>17</v>
@@ -6225,19 +5472,19 @@
         <v>11</v>
       </c>
       <c r="B159" t="s">
-        <v>389</v>
+        <v>307</v>
       </c>
       <c r="C159" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="E159" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G159" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I159" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K159" t="s">
         <v>17</v>
@@ -6248,19 +5495,19 @@
         <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>562</v>
+        <v>453</v>
       </c>
       <c r="C160" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="E160" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G160" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I160" t="s">
-        <v>558</v>
+        <v>449</v>
       </c>
       <c r="K160" t="s">
         <v>17</v>
@@ -6271,19 +5518,19 @@
         <v>11</v>
       </c>
       <c r="B161" t="s">
-        <v>390</v>
+        <v>308</v>
       </c>
       <c r="C161" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="E161" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G161" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I161" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K161" t="s">
         <v>17</v>
@@ -6294,19 +5541,19 @@
         <v>11</v>
       </c>
       <c r="B162" t="s">
-        <v>391</v>
+        <v>309</v>
       </c>
       <c r="C162" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="E162" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G162" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I162" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K162" t="s">
         <v>17</v>
@@ -6317,19 +5564,19 @@
         <v>11</v>
       </c>
       <c r="B163" t="s">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="C163" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="E163" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G163" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I163" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K163" t="s">
         <v>17</v>
@@ -6340,19 +5587,19 @@
         <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>584</v>
+        <v>464</v>
       </c>
       <c r="C164" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="E164" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G164" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I164" t="s">
-        <v>558</v>
+        <v>449</v>
       </c>
       <c r="K164" t="s">
         <v>17</v>
@@ -6363,19 +5610,19 @@
         <v>11</v>
       </c>
       <c r="B165" t="s">
-        <v>393</v>
+        <v>311</v>
       </c>
       <c r="C165" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="E165" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G165" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I165" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K165" t="s">
         <v>17</v>
@@ -6386,19 +5633,19 @@
         <v>11</v>
       </c>
       <c r="B166" t="s">
-        <v>394</v>
+        <v>312</v>
       </c>
       <c r="C166" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="E166" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G166" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I166" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K166" t="s">
         <v>17</v>
@@ -6409,19 +5656,19 @@
         <v>11</v>
       </c>
       <c r="B167" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
       <c r="C167" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="E167" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G167" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I167" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K167" t="s">
         <v>17</v>
@@ -6432,19 +5679,19 @@
         <v>11</v>
       </c>
       <c r="B168" t="s">
-        <v>396</v>
+        <v>314</v>
       </c>
       <c r="C168" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="E168" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G168" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I168" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K168" t="s">
         <v>17</v>
@@ -6455,19 +5702,19 @@
         <v>11</v>
       </c>
       <c r="B169" t="s">
-        <v>560</v>
+        <v>451</v>
       </c>
       <c r="C169" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="E169" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G169" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I169" t="s">
-        <v>558</v>
+        <v>449</v>
       </c>
       <c r="K169" t="s">
         <v>17</v>
@@ -6478,19 +5725,19 @@
         <v>11</v>
       </c>
       <c r="B170" t="s">
-        <v>557</v>
+        <v>448</v>
       </c>
       <c r="C170" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="E170" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G170" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I170" t="s">
-        <v>555</v>
+        <v>446</v>
       </c>
       <c r="K170" t="s">
         <v>17</v>
@@ -6501,19 +5748,19 @@
         <v>11</v>
       </c>
       <c r="B171" t="s">
-        <v>397</v>
+        <v>315</v>
       </c>
       <c r="C171" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="E171" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G171" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I171" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K171" t="s">
         <v>17</v>
@@ -6524,19 +5771,19 @@
         <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>380</v>
+        <v>299</v>
       </c>
       <c r="C172" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="E172" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G172" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I172" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K172" t="s">
         <v>17</v>
@@ -6547,19 +5794,19 @@
         <v>11</v>
       </c>
       <c r="B173" t="s">
-        <v>401</v>
+        <v>316</v>
       </c>
       <c r="C173" t="s">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="E173" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G173" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I173" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K173" t="s">
         <v>17</v>
@@ -6570,19 +5817,19 @@
         <v>11</v>
       </c>
       <c r="B174" t="s">
-        <v>381</v>
+        <v>300</v>
       </c>
       <c r="C174" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="E174" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G174" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I174" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K174" t="s">
         <v>17</v>
@@ -6593,19 +5840,19 @@
         <v>11</v>
       </c>
       <c r="B175" t="s">
-        <v>561</v>
+        <v>452</v>
       </c>
       <c r="C175" t="s">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="E175" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G175" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I175" t="s">
-        <v>554</v>
+        <v>445</v>
       </c>
       <c r="K175" t="s">
         <v>17</v>
@@ -6616,19 +5863,19 @@
         <v>11</v>
       </c>
       <c r="B176" t="s">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="C176" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="E176" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G176" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I176" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K176" t="s">
         <v>17</v>
@@ -6639,19 +5886,19 @@
         <v>11</v>
       </c>
       <c r="B177" t="s">
-        <v>403</v>
+        <v>318</v>
       </c>
       <c r="C177" t="s">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="E177" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G177" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I177" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K177" t="s">
         <v>17</v>
@@ -6662,19 +5909,19 @@
         <v>11</v>
       </c>
       <c r="B178" t="s">
-        <v>404</v>
+        <v>319</v>
       </c>
       <c r="C178" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="E178" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G178" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I178" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K178" t="s">
         <v>17</v>
@@ -6685,19 +5932,19 @@
         <v>11</v>
       </c>
       <c r="B179" t="s">
-        <v>405</v>
+        <v>320</v>
       </c>
       <c r="C179" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="E179" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G179" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I179" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K179" t="s">
         <v>17</v>
@@ -6708,19 +5955,19 @@
         <v>11</v>
       </c>
       <c r="B180" t="s">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="C180" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E180" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G180" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I180" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K180" t="s">
         <v>17</v>
@@ -6731,19 +5978,19 @@
         <v>11</v>
       </c>
       <c r="B181" t="s">
-        <v>383</v>
+        <v>302</v>
       </c>
       <c r="C181" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="E181" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G181" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I181" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K181" t="s">
         <v>17</v>
@@ -6754,44 +6001,44 @@
         <v>11</v>
       </c>
       <c r="B182" t="s">
-        <v>384</v>
+        <v>303</v>
       </c>
       <c r="C182" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="E182" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="G182" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I182" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K182" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E183" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G183" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I183" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K183" s="6" t="s">
+    <row r="183" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I183" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="K183" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6800,28 +6047,28 @@
         <v>11</v>
       </c>
       <c r="B184" t="s">
-        <v>525</v>
+        <v>416</v>
       </c>
       <c r="C184" t="s">
-        <v>526</v>
+        <v>417</v>
       </c>
       <c r="E184" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F184" t="s">
-        <v>527</v>
+        <v>418</v>
       </c>
       <c r="G184" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H184" t="s">
-        <v>525</v>
+        <v>416</v>
       </c>
       <c r="I184" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K184" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
@@ -6829,28 +6076,28 @@
         <v>11</v>
       </c>
       <c r="B185" t="s">
-        <v>531</v>
+        <v>422</v>
       </c>
       <c r="C185" t="s">
-        <v>532</v>
+        <v>423</v>
       </c>
       <c r="E185" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F185" t="s">
-        <v>533</v>
+        <v>424</v>
       </c>
       <c r="G185" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H185" t="s">
-        <v>531</v>
+        <v>422</v>
       </c>
       <c r="I185" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K185" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
@@ -6858,28 +6105,28 @@
         <v>11</v>
       </c>
       <c r="B186" t="s">
-        <v>534</v>
+        <v>425</v>
       </c>
       <c r="C186" t="s">
-        <v>535</v>
+        <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F186" t="s">
-        <v>536</v>
+        <v>427</v>
       </c>
       <c r="G186" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H186" t="s">
-        <v>534</v>
+        <v>425</v>
       </c>
       <c r="I186" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K186" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
@@ -6887,28 +6134,28 @@
         <v>11</v>
       </c>
       <c r="B187" t="s">
-        <v>537</v>
+        <v>428</v>
       </c>
       <c r="C187" t="s">
-        <v>538</v>
+        <v>429</v>
       </c>
       <c r="E187" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F187" t="s">
-        <v>539</v>
+        <v>430</v>
       </c>
       <c r="G187" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H187" t="s">
-        <v>537</v>
+        <v>428</v>
       </c>
       <c r="I187" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K187" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
@@ -6916,28 +6163,28 @@
         <v>11</v>
       </c>
       <c r="B188" t="s">
-        <v>540</v>
+        <v>431</v>
       </c>
       <c r="C188" t="s">
-        <v>541</v>
+        <v>432</v>
       </c>
       <c r="E188" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F188" t="s">
-        <v>542</v>
+        <v>433</v>
       </c>
       <c r="G188" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H188" t="s">
-        <v>540</v>
+        <v>431</v>
       </c>
       <c r="I188" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K188" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
@@ -6945,28 +6192,28 @@
         <v>11</v>
       </c>
       <c r="B189" t="s">
-        <v>543</v>
+        <v>434</v>
       </c>
       <c r="C189" t="s">
-        <v>544</v>
+        <v>435</v>
       </c>
       <c r="E189" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F189" t="s">
-        <v>545</v>
+        <v>436</v>
       </c>
       <c r="G189" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H189" t="s">
-        <v>543</v>
+        <v>434</v>
       </c>
       <c r="I189" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K189" t="s">
-        <v>530</v>
+        <v>421</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
@@ -6974,57 +6221,57 @@
         <v>11</v>
       </c>
       <c r="B190" t="s">
-        <v>546</v>
+        <v>437</v>
       </c>
       <c r="C190" t="s">
-        <v>547</v>
+        <v>438</v>
       </c>
       <c r="E190" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="F190" t="s">
-        <v>548</v>
+        <v>439</v>
       </c>
       <c r="G190" t="s">
-        <v>528</v>
+        <v>419</v>
       </c>
       <c r="H190" t="s">
-        <v>546</v>
+        <v>437</v>
       </c>
       <c r="I190" t="s">
-        <v>529</v>
+        <v>420</v>
       </c>
       <c r="K190" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>551</v>
-      </c>
-      <c r="G191" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="H191" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="I191" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="K191" s="6" t="s">
-        <v>530</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I191" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K191" s="5" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
@@ -7032,28 +6279,28 @@
         <v>11</v>
       </c>
       <c r="B192" t="s">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="C192" t="s">
-        <v>566</v>
+        <v>456</v>
       </c>
       <c r="D192" t="s">
-        <v>567</v>
+        <v>457</v>
       </c>
       <c r="E192" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="F192" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="G192" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="I192" t="s">
-        <v>568</v>
+        <v>458</v>
       </c>
       <c r="K192" t="s">
-        <v>569</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
@@ -7061,19 +6308,19 @@
         <v>11</v>
       </c>
       <c r="B193" t="s">
-        <v>581</v>
+        <v>461</v>
       </c>
       <c r="C193" t="s">
-        <v>582</v>
+        <v>462</v>
       </c>
       <c r="E193" t="s">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="G193" t="s">
-        <v>591</v>
+        <v>468</v>
       </c>
       <c r="K193" t="s">
-        <v>583</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
@@ -7081,16 +6328,16 @@
         <v>11</v>
       </c>
       <c r="B194" t="s">
-        <v>588</v>
+        <v>465</v>
       </c>
       <c r="C194" t="s">
-        <v>589</v>
+        <v>466</v>
       </c>
       <c r="E194" t="s">
-        <v>590</v>
+        <v>467</v>
       </c>
       <c r="G194" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="K194" t="s">
         <v>17</v>
@@ -7131,2592 +6378,4 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66CA64A-CF66-F949-A75A-AE58021850F7}">
-  <dimension ref="A1:L105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G3" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" t="s">
-        <v>203</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>440</v>
-      </c>
-      <c r="C4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" t="s">
-        <v>315</v>
-      </c>
-      <c r="G4" t="s">
-        <v>171</v>
-      </c>
-      <c r="I4" t="s">
-        <v>188</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C5" t="s">
-        <v>321</v>
-      </c>
-      <c r="E5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" t="s">
-        <v>320</v>
-      </c>
-      <c r="G5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5" t="s">
-        <v>188</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>573</v>
-      </c>
-      <c r="C6" t="s">
-        <v>571</v>
-      </c>
-      <c r="E6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" t="s">
-        <v>572</v>
-      </c>
-      <c r="K6" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>633</v>
-      </c>
-      <c r="C7" t="s">
-        <v>634</v>
-      </c>
-      <c r="E7" t="s">
-        <v>607</v>
-      </c>
-      <c r="G7" t="s">
-        <v>607</v>
-      </c>
-      <c r="H7" t="s">
-        <v>635</v>
-      </c>
-      <c r="J7" t="s">
-        <v>609</v>
-      </c>
-      <c r="K7" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>636</v>
-      </c>
-      <c r="C8" t="s">
-        <v>637</v>
-      </c>
-      <c r="E8" t="s">
-        <v>607</v>
-      </c>
-      <c r="G8" t="s">
-        <v>607</v>
-      </c>
-      <c r="H8" t="s">
-        <v>635</v>
-      </c>
-      <c r="J8" t="s">
-        <v>609</v>
-      </c>
-      <c r="K8" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C9" t="s">
-        <v>639</v>
-      </c>
-      <c r="E9" t="s">
-        <v>607</v>
-      </c>
-      <c r="G9" t="s">
-        <v>607</v>
-      </c>
-      <c r="H9" t="s">
-        <v>635</v>
-      </c>
-      <c r="J9" t="s">
-        <v>609</v>
-      </c>
-      <c r="K9" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>655</v>
-      </c>
-      <c r="C10" t="s">
-        <v>656</v>
-      </c>
-      <c r="E10" t="s">
-        <v>607</v>
-      </c>
-      <c r="G10" t="s">
-        <v>607</v>
-      </c>
-      <c r="H10" t="s">
-        <v>657</v>
-      </c>
-      <c r="J10" t="s">
-        <v>609</v>
-      </c>
-      <c r="K10" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>703</v>
-      </c>
-      <c r="C11" t="s">
-        <v>600</v>
-      </c>
-      <c r="E11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G11" t="s">
-        <v>595</v>
-      </c>
-      <c r="H11" t="s">
-        <v>597</v>
-      </c>
-      <c r="I11" t="s">
-        <v>188</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K11" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>577</v>
-      </c>
-      <c r="C12" t="s">
-        <v>574</v>
-      </c>
-      <c r="E12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G12" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" t="s">
-        <v>169</v>
-      </c>
-      <c r="I12" t="s">
-        <v>572</v>
-      </c>
-      <c r="K12" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>578</v>
-      </c>
-      <c r="C13" t="s">
-        <v>575</v>
-      </c>
-      <c r="E13" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G13" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" t="s">
-        <v>169</v>
-      </c>
-      <c r="I13" t="s">
-        <v>572</v>
-      </c>
-      <c r="K13" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>579</v>
-      </c>
-      <c r="C14" t="s">
-        <v>576</v>
-      </c>
-      <c r="E14" t="s">
-        <v>169</v>
-      </c>
-      <c r="F14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" t="s">
-        <v>169</v>
-      </c>
-      <c r="I14" t="s">
-        <v>572</v>
-      </c>
-      <c r="K14" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>587</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="E15" t="s">
-        <v>169</v>
-      </c>
-      <c r="F15" t="s">
-        <v>168</v>
-      </c>
-      <c r="G15" t="s">
-        <v>169</v>
-      </c>
-      <c r="H15" t="s">
-        <v>169</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>605</v>
-      </c>
-      <c r="C16" t="s">
-        <v>606</v>
-      </c>
-      <c r="E16" t="s">
-        <v>607</v>
-      </c>
-      <c r="G16" t="s">
-        <v>607</v>
-      </c>
-      <c r="H16" t="s">
-        <v>608</v>
-      </c>
-      <c r="J16" t="s">
-        <v>609</v>
-      </c>
-      <c r="K16" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>610</v>
-      </c>
-      <c r="C17" t="s">
-        <v>611</v>
-      </c>
-      <c r="E17" t="s">
-        <v>607</v>
-      </c>
-      <c r="G17" t="s">
-        <v>607</v>
-      </c>
-      <c r="H17" t="s">
-        <v>612</v>
-      </c>
-      <c r="J17" t="s">
-        <v>609</v>
-      </c>
-      <c r="K17" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>613</v>
-      </c>
-      <c r="C18" t="s">
-        <v>614</v>
-      </c>
-      <c r="E18" t="s">
-        <v>607</v>
-      </c>
-      <c r="G18" t="s">
-        <v>607</v>
-      </c>
-      <c r="H18" t="s">
-        <v>612</v>
-      </c>
-      <c r="J18" t="s">
-        <v>609</v>
-      </c>
-      <c r="K18" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" t="s">
-        <v>616</v>
-      </c>
-      <c r="E19" t="s">
-        <v>607</v>
-      </c>
-      <c r="G19" t="s">
-        <v>607</v>
-      </c>
-      <c r="H19" t="s">
-        <v>617</v>
-      </c>
-      <c r="J19" t="s">
-        <v>609</v>
-      </c>
-      <c r="K19" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>618</v>
-      </c>
-      <c r="C20" t="s">
-        <v>619</v>
-      </c>
-      <c r="E20" t="s">
-        <v>607</v>
-      </c>
-      <c r="G20" t="s">
-        <v>607</v>
-      </c>
-      <c r="H20" t="s">
-        <v>617</v>
-      </c>
-      <c r="J20" t="s">
-        <v>609</v>
-      </c>
-      <c r="K20" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>620</v>
-      </c>
-      <c r="C21" t="s">
-        <v>621</v>
-      </c>
-      <c r="E21" t="s">
-        <v>607</v>
-      </c>
-      <c r="G21" t="s">
-        <v>607</v>
-      </c>
-      <c r="H21" t="s">
-        <v>617</v>
-      </c>
-      <c r="J21" t="s">
-        <v>609</v>
-      </c>
-      <c r="K21" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>622</v>
-      </c>
-      <c r="C22" t="s">
-        <v>623</v>
-      </c>
-      <c r="E22" t="s">
-        <v>607</v>
-      </c>
-      <c r="G22" t="s">
-        <v>607</v>
-      </c>
-      <c r="H22" t="s">
-        <v>617</v>
-      </c>
-      <c r="J22" t="s">
-        <v>609</v>
-      </c>
-      <c r="K22" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" t="s">
-        <v>624</v>
-      </c>
-      <c r="C23" t="s">
-        <v>625</v>
-      </c>
-      <c r="E23" t="s">
-        <v>607</v>
-      </c>
-      <c r="G23" t="s">
-        <v>607</v>
-      </c>
-      <c r="H23" t="s">
-        <v>617</v>
-      </c>
-      <c r="J23" t="s">
-        <v>609</v>
-      </c>
-      <c r="K23" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>626</v>
-      </c>
-      <c r="C24" t="s">
-        <v>627</v>
-      </c>
-      <c r="E24" t="s">
-        <v>607</v>
-      </c>
-      <c r="G24" t="s">
-        <v>607</v>
-      </c>
-      <c r="H24" t="s">
-        <v>628</v>
-      </c>
-      <c r="J24" t="s">
-        <v>609</v>
-      </c>
-      <c r="K24" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
-        <v>629</v>
-      </c>
-      <c r="C25" t="s">
-        <v>630</v>
-      </c>
-      <c r="E25" t="s">
-        <v>607</v>
-      </c>
-      <c r="G25" t="s">
-        <v>607</v>
-      </c>
-      <c r="H25" t="s">
-        <v>628</v>
-      </c>
-      <c r="J25" t="s">
-        <v>609</v>
-      </c>
-      <c r="K25" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" t="s">
-        <v>631</v>
-      </c>
-      <c r="C26" t="s">
-        <v>632</v>
-      </c>
-      <c r="E26" t="s">
-        <v>607</v>
-      </c>
-      <c r="G26" t="s">
-        <v>607</v>
-      </c>
-      <c r="H26" t="s">
-        <v>628</v>
-      </c>
-      <c r="J26" t="s">
-        <v>609</v>
-      </c>
-      <c r="K26" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>640</v>
-      </c>
-      <c r="C27" t="s">
-        <v>641</v>
-      </c>
-      <c r="E27" t="s">
-        <v>607</v>
-      </c>
-      <c r="G27" t="s">
-        <v>607</v>
-      </c>
-      <c r="H27" t="s">
-        <v>642</v>
-      </c>
-      <c r="J27" t="s">
-        <v>609</v>
-      </c>
-      <c r="K27" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>643</v>
-      </c>
-      <c r="C28" t="s">
-        <v>644</v>
-      </c>
-      <c r="E28" t="s">
-        <v>607</v>
-      </c>
-      <c r="G28" t="s">
-        <v>607</v>
-      </c>
-      <c r="H28" t="s">
-        <v>642</v>
-      </c>
-      <c r="J28" t="s">
-        <v>609</v>
-      </c>
-      <c r="K28" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>645</v>
-      </c>
-      <c r="C29" t="s">
-        <v>646</v>
-      </c>
-      <c r="E29" t="s">
-        <v>607</v>
-      </c>
-      <c r="G29" t="s">
-        <v>607</v>
-      </c>
-      <c r="H29" t="s">
-        <v>642</v>
-      </c>
-      <c r="J29" t="s">
-        <v>609</v>
-      </c>
-      <c r="K29" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>647</v>
-      </c>
-      <c r="C30" t="s">
-        <v>648</v>
-      </c>
-      <c r="E30" t="s">
-        <v>607</v>
-      </c>
-      <c r="G30" t="s">
-        <v>607</v>
-      </c>
-      <c r="H30" t="s">
-        <v>649</v>
-      </c>
-      <c r="J30" t="s">
-        <v>609</v>
-      </c>
-      <c r="K30" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
-        <v>650</v>
-      </c>
-      <c r="C31" t="s">
-        <v>651</v>
-      </c>
-      <c r="E31" t="s">
-        <v>607</v>
-      </c>
-      <c r="G31" t="s">
-        <v>607</v>
-      </c>
-      <c r="H31" t="s">
-        <v>649</v>
-      </c>
-      <c r="J31" t="s">
-        <v>609</v>
-      </c>
-      <c r="K31" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
-        <v>652</v>
-      </c>
-      <c r="C32" t="s">
-        <v>653</v>
-      </c>
-      <c r="E32" t="s">
-        <v>607</v>
-      </c>
-      <c r="G32" t="s">
-        <v>607</v>
-      </c>
-      <c r="H32" t="s">
-        <v>654</v>
-      </c>
-      <c r="J32" t="s">
-        <v>609</v>
-      </c>
-      <c r="K32" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>375</v>
-      </c>
-      <c r="C33" t="s">
-        <v>268</v>
-      </c>
-      <c r="E33" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" t="s">
-        <v>166</v>
-      </c>
-      <c r="I33" t="s">
-        <v>203</v>
-      </c>
-      <c r="K33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
-        <v>339</v>
-      </c>
-      <c r="C34" t="s">
-        <v>231</v>
-      </c>
-      <c r="E34" t="s">
-        <v>166</v>
-      </c>
-      <c r="G34" t="s">
-        <v>166</v>
-      </c>
-      <c r="I34" t="s">
-        <v>203</v>
-      </c>
-      <c r="K34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" t="s">
-        <v>463</v>
-      </c>
-      <c r="C35" t="s">
-        <v>708</v>
-      </c>
-      <c r="E35" t="s">
-        <v>464</v>
-      </c>
-      <c r="G35" t="s">
-        <v>464</v>
-      </c>
-      <c r="I35" t="s">
-        <v>448</v>
-      </c>
-      <c r="K35" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" t="s">
-        <v>659</v>
-      </c>
-      <c r="E36" t="s">
-        <v>660</v>
-      </c>
-      <c r="G36" t="s">
-        <v>660</v>
-      </c>
-      <c r="H36" t="s">
-        <v>661</v>
-      </c>
-      <c r="J36" t="s">
-        <v>609</v>
-      </c>
-      <c r="K36" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>662</v>
-      </c>
-      <c r="C37" t="s">
-        <v>663</v>
-      </c>
-      <c r="E37" t="s">
-        <v>660</v>
-      </c>
-      <c r="G37" t="s">
-        <v>660</v>
-      </c>
-      <c r="H37" t="s">
-        <v>661</v>
-      </c>
-      <c r="J37" t="s">
-        <v>609</v>
-      </c>
-      <c r="K37" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" t="s">
-        <v>664</v>
-      </c>
-      <c r="C38" t="s">
-        <v>665</v>
-      </c>
-      <c r="E38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G38" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" t="s">
-        <v>666</v>
-      </c>
-      <c r="J38" t="s">
-        <v>609</v>
-      </c>
-      <c r="K38" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" t="s">
-        <v>667</v>
-      </c>
-      <c r="C39" t="s">
-        <v>668</v>
-      </c>
-      <c r="E39" t="s">
-        <v>38</v>
-      </c>
-      <c r="G39" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" t="s">
-        <v>666</v>
-      </c>
-      <c r="J39" t="s">
-        <v>609</v>
-      </c>
-      <c r="K39" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" t="s">
-        <v>669</v>
-      </c>
-      <c r="C40" t="s">
-        <v>670</v>
-      </c>
-      <c r="E40" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" t="s">
-        <v>38</v>
-      </c>
-      <c r="H40" t="s">
-        <v>666</v>
-      </c>
-      <c r="J40" t="s">
-        <v>609</v>
-      </c>
-      <c r="K40" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" t="s">
-        <v>671</v>
-      </c>
-      <c r="C41" t="s">
-        <v>672</v>
-      </c>
-      <c r="E41" t="s">
-        <v>38</v>
-      </c>
-      <c r="G41" t="s">
-        <v>38</v>
-      </c>
-      <c r="H41" t="s">
-        <v>666</v>
-      </c>
-      <c r="J41" t="s">
-        <v>609</v>
-      </c>
-      <c r="K41" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" t="s">
-        <v>673</v>
-      </c>
-      <c r="C42" t="s">
-        <v>674</v>
-      </c>
-      <c r="E42" t="s">
-        <v>38</v>
-      </c>
-      <c r="G42" t="s">
-        <v>38</v>
-      </c>
-      <c r="H42" t="s">
-        <v>675</v>
-      </c>
-      <c r="J42" t="s">
-        <v>609</v>
-      </c>
-      <c r="K42" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" t="s">
-        <v>676</v>
-      </c>
-      <c r="C43" t="s">
-        <v>677</v>
-      </c>
-      <c r="E43" t="s">
-        <v>38</v>
-      </c>
-      <c r="G43" t="s">
-        <v>38</v>
-      </c>
-      <c r="H43" t="s">
-        <v>678</v>
-      </c>
-      <c r="J43" t="s">
-        <v>609</v>
-      </c>
-      <c r="K43" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" t="s">
-        <v>679</v>
-      </c>
-      <c r="C44" t="s">
-        <v>680</v>
-      </c>
-      <c r="E44" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" t="s">
-        <v>38</v>
-      </c>
-      <c r="H44" t="s">
-        <v>681</v>
-      </c>
-      <c r="J44" t="s">
-        <v>609</v>
-      </c>
-      <c r="K44" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
-        <v>682</v>
-      </c>
-      <c r="C45" t="s">
-        <v>683</v>
-      </c>
-      <c r="E45" t="s">
-        <v>139</v>
-      </c>
-      <c r="G45" t="s">
-        <v>139</v>
-      </c>
-      <c r="H45" t="s">
-        <v>684</v>
-      </c>
-      <c r="J45" t="s">
-        <v>609</v>
-      </c>
-      <c r="K45" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
-        <v>685</v>
-      </c>
-      <c r="C46" t="s">
-        <v>686</v>
-      </c>
-      <c r="E46" t="s">
-        <v>139</v>
-      </c>
-      <c r="G46" t="s">
-        <v>139</v>
-      </c>
-      <c r="H46" t="s">
-        <v>687</v>
-      </c>
-      <c r="J46" t="s">
-        <v>609</v>
-      </c>
-      <c r="K46" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" t="s">
-        <v>688</v>
-      </c>
-      <c r="C47" t="s">
-        <v>689</v>
-      </c>
-      <c r="E47" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" t="s">
-        <v>139</v>
-      </c>
-      <c r="H47" t="s">
-        <v>690</v>
-      </c>
-      <c r="J47" t="s">
-        <v>609</v>
-      </c>
-      <c r="K47" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" t="s">
-        <v>691</v>
-      </c>
-      <c r="C48" t="s">
-        <v>692</v>
-      </c>
-      <c r="E48" t="s">
-        <v>139</v>
-      </c>
-      <c r="G48" t="s">
-        <v>139</v>
-      </c>
-      <c r="H48" t="s">
-        <v>693</v>
-      </c>
-      <c r="J48" t="s">
-        <v>609</v>
-      </c>
-      <c r="K48" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" t="s">
-        <v>694</v>
-      </c>
-      <c r="C49" t="s">
-        <v>695</v>
-      </c>
-      <c r="E49" t="s">
-        <v>139</v>
-      </c>
-      <c r="G49" t="s">
-        <v>139</v>
-      </c>
-      <c r="H49" t="s">
-        <v>693</v>
-      </c>
-      <c r="J49" t="s">
-        <v>609</v>
-      </c>
-      <c r="K49" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s">
-        <v>696</v>
-      </c>
-      <c r="C50" t="s">
-        <v>697</v>
-      </c>
-      <c r="E50" t="s">
-        <v>139</v>
-      </c>
-      <c r="G50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H50" t="s">
-        <v>693</v>
-      </c>
-      <c r="J50" t="s">
-        <v>609</v>
-      </c>
-      <c r="K50" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>11</v>
-      </c>
-      <c r="B51" t="s">
-        <v>698</v>
-      </c>
-      <c r="C51" t="s">
-        <v>699</v>
-      </c>
-      <c r="E51" t="s">
-        <v>139</v>
-      </c>
-      <c r="G51" t="s">
-        <v>139</v>
-      </c>
-      <c r="H51" t="s">
-        <v>693</v>
-      </c>
-      <c r="J51" t="s">
-        <v>609</v>
-      </c>
-      <c r="K51" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B53" t="s">
-        <v>151</v>
-      </c>
-      <c r="C53" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" t="s">
-        <v>139</v>
-      </c>
-      <c r="G53" t="s">
-        <v>139</v>
-      </c>
-      <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" t="s">
-        <v>700</v>
-      </c>
-      <c r="C54" t="s">
-        <v>596</v>
-      </c>
-      <c r="E54" t="s">
-        <v>166</v>
-      </c>
-      <c r="G54" t="s">
-        <v>595</v>
-      </c>
-      <c r="H54" t="s">
-        <v>597</v>
-      </c>
-      <c r="I54" t="s">
-        <v>188</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K54" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" t="s">
-        <v>701</v>
-      </c>
-      <c r="C55" t="s">
-        <v>598</v>
-      </c>
-      <c r="E55" t="s">
-        <v>166</v>
-      </c>
-      <c r="G55" t="s">
-        <v>595</v>
-      </c>
-      <c r="H55" t="s">
-        <v>597</v>
-      </c>
-      <c r="I55" t="s">
-        <v>188</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K55" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" t="s">
-        <v>702</v>
-      </c>
-      <c r="C56" t="s">
-        <v>599</v>
-      </c>
-      <c r="E56" t="s">
-        <v>166</v>
-      </c>
-      <c r="G56" t="s">
-        <v>595</v>
-      </c>
-      <c r="H56" t="s">
-        <v>597</v>
-      </c>
-      <c r="I56" t="s">
-        <v>188</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K56" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" t="s">
-        <v>704</v>
-      </c>
-      <c r="C57" t="s">
-        <v>601</v>
-      </c>
-      <c r="E57" t="s">
-        <v>166</v>
-      </c>
-      <c r="G57" t="s">
-        <v>595</v>
-      </c>
-      <c r="H57" t="s">
-        <v>597</v>
-      </c>
-      <c r="I57" t="s">
-        <v>188</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K57" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s">
-        <v>705</v>
-      </c>
-      <c r="C58" t="s">
-        <v>602</v>
-      </c>
-      <c r="E58" t="s">
-        <v>166</v>
-      </c>
-      <c r="G58" t="s">
-        <v>595</v>
-      </c>
-      <c r="H58" t="s">
-        <v>597</v>
-      </c>
-      <c r="I58" t="s">
-        <v>188</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K58" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" t="s">
-        <v>706</v>
-      </c>
-      <c r="C59" t="s">
-        <v>603</v>
-      </c>
-      <c r="E59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G59" t="s">
-        <v>595</v>
-      </c>
-      <c r="H59" t="s">
-        <v>597</v>
-      </c>
-      <c r="I59" t="s">
-        <v>188</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K59" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" t="s">
-        <v>707</v>
-      </c>
-      <c r="C60" t="s">
-        <v>604</v>
-      </c>
-      <c r="E60" t="s">
-        <v>166</v>
-      </c>
-      <c r="G60" t="s">
-        <v>595</v>
-      </c>
-      <c r="H60" t="s">
-        <v>597</v>
-      </c>
-      <c r="I60" t="s">
-        <v>188</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="K60" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" t="s">
-        <v>426</v>
-      </c>
-      <c r="C61" t="s">
-        <v>307</v>
-      </c>
-      <c r="E61" t="s">
-        <v>170</v>
-      </c>
-      <c r="G61" t="s">
-        <v>171</v>
-      </c>
-      <c r="I61" t="s">
-        <v>297</v>
-      </c>
-      <c r="K61" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" t="s">
-        <v>428</v>
-      </c>
-      <c r="C62" t="s">
-        <v>309</v>
-      </c>
-      <c r="E62" t="s">
-        <v>170</v>
-      </c>
-      <c r="G62" t="s">
-        <v>171</v>
-      </c>
-      <c r="I62" t="s">
-        <v>297</v>
-      </c>
-      <c r="K62" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" t="s">
-        <v>421</v>
-      </c>
-      <c r="C63" t="s">
-        <v>302</v>
-      </c>
-      <c r="E63" t="s">
-        <v>170</v>
-      </c>
-      <c r="G63" t="s">
-        <v>171</v>
-      </c>
-      <c r="I63" t="s">
-        <v>297</v>
-      </c>
-      <c r="K63" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" t="s">
-        <v>417</v>
-      </c>
-      <c r="C64" t="s">
-        <v>296</v>
-      </c>
-      <c r="E64" t="s">
-        <v>170</v>
-      </c>
-      <c r="G64" t="s">
-        <v>171</v>
-      </c>
-      <c r="I64" t="s">
-        <v>297</v>
-      </c>
-      <c r="K64" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" t="s">
-        <v>425</v>
-      </c>
-      <c r="C65" t="s">
-        <v>306</v>
-      </c>
-      <c r="E65" t="s">
-        <v>170</v>
-      </c>
-      <c r="G65" t="s">
-        <v>171</v>
-      </c>
-      <c r="I65" t="s">
-        <v>297</v>
-      </c>
-      <c r="K65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s">
-        <v>427</v>
-      </c>
-      <c r="C66" t="s">
-        <v>308</v>
-      </c>
-      <c r="E66" t="s">
-        <v>170</v>
-      </c>
-      <c r="G66" t="s">
-        <v>171</v>
-      </c>
-      <c r="I66" t="s">
-        <v>297</v>
-      </c>
-      <c r="K66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" t="s">
-        <v>429</v>
-      </c>
-      <c r="C67" t="s">
-        <v>310</v>
-      </c>
-      <c r="E67" t="s">
-        <v>170</v>
-      </c>
-      <c r="G67" t="s">
-        <v>171</v>
-      </c>
-      <c r="I67" t="s">
-        <v>297</v>
-      </c>
-      <c r="K67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" t="s">
-        <v>430</v>
-      </c>
-      <c r="C68" t="s">
-        <v>311</v>
-      </c>
-      <c r="E68" t="s">
-        <v>170</v>
-      </c>
-      <c r="G68" t="s">
-        <v>171</v>
-      </c>
-      <c r="I68" t="s">
-        <v>297</v>
-      </c>
-      <c r="K68" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" t="s">
-        <v>419</v>
-      </c>
-      <c r="C69" t="s">
-        <v>300</v>
-      </c>
-      <c r="E69" t="s">
-        <v>170</v>
-      </c>
-      <c r="G69" t="s">
-        <v>171</v>
-      </c>
-      <c r="I69" t="s">
-        <v>297</v>
-      </c>
-      <c r="K69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
-        <v>420</v>
-      </c>
-      <c r="C70" t="s">
-        <v>301</v>
-      </c>
-      <c r="E70" t="s">
-        <v>170</v>
-      </c>
-      <c r="G70" t="s">
-        <v>171</v>
-      </c>
-      <c r="I70" t="s">
-        <v>297</v>
-      </c>
-      <c r="K70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" t="s">
-        <v>422</v>
-      </c>
-      <c r="C71" t="s">
-        <v>303</v>
-      </c>
-      <c r="E71" t="s">
-        <v>170</v>
-      </c>
-      <c r="G71" t="s">
-        <v>171</v>
-      </c>
-      <c r="I71" t="s">
-        <v>297</v>
-      </c>
-      <c r="K71" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>423</v>
-      </c>
-      <c r="C72" t="s">
-        <v>304</v>
-      </c>
-      <c r="E72" t="s">
-        <v>170</v>
-      </c>
-      <c r="G72" t="s">
-        <v>171</v>
-      </c>
-      <c r="I72" t="s">
-        <v>297</v>
-      </c>
-      <c r="K72" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>11</v>
-      </c>
-      <c r="B73" t="s">
-        <v>424</v>
-      </c>
-      <c r="C73" t="s">
-        <v>305</v>
-      </c>
-      <c r="E73" t="s">
-        <v>170</v>
-      </c>
-      <c r="G73" t="s">
-        <v>171</v>
-      </c>
-      <c r="I73" t="s">
-        <v>297</v>
-      </c>
-      <c r="K73" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" t="s">
-        <v>76</v>
-      </c>
-      <c r="G74" t="s">
-        <v>76</v>
-      </c>
-      <c r="H74" t="s">
-        <v>88</v>
-      </c>
-      <c r="K74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" t="s">
-        <v>91</v>
-      </c>
-      <c r="C75" t="s">
-        <v>92</v>
-      </c>
-      <c r="E75" t="s">
-        <v>76</v>
-      </c>
-      <c r="G75" t="s">
-        <v>76</v>
-      </c>
-      <c r="H75" t="s">
-        <v>88</v>
-      </c>
-      <c r="K75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" t="s">
-        <v>94</v>
-      </c>
-      <c r="E76" t="s">
-        <v>76</v>
-      </c>
-      <c r="G76" t="s">
-        <v>76</v>
-      </c>
-      <c r="H76" t="s">
-        <v>88</v>
-      </c>
-      <c r="K76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G77" t="s">
-        <v>76</v>
-      </c>
-      <c r="H77" t="s">
-        <v>88</v>
-      </c>
-      <c r="K77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" t="s">
-        <v>407</v>
-      </c>
-      <c r="C78" t="s">
-        <v>189</v>
-      </c>
-      <c r="E78" t="s">
-        <v>169</v>
-      </c>
-      <c r="G78" t="s">
-        <v>167</v>
-      </c>
-      <c r="H78" t="s">
-        <v>169</v>
-      </c>
-      <c r="I78" t="s">
-        <v>190</v>
-      </c>
-      <c r="K78" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79" t="s">
-        <v>331</v>
-      </c>
-      <c r="C79" t="s">
-        <v>222</v>
-      </c>
-      <c r="E79" t="s">
-        <v>166</v>
-      </c>
-      <c r="G79" t="s">
-        <v>166</v>
-      </c>
-      <c r="I79" t="s">
-        <v>203</v>
-      </c>
-      <c r="K79" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>11</v>
-      </c>
-      <c r="B80" t="s">
-        <v>332</v>
-      </c>
-      <c r="C80" t="s">
-        <v>223</v>
-      </c>
-      <c r="E80" t="s">
-        <v>166</v>
-      </c>
-      <c r="G80" t="s">
-        <v>166</v>
-      </c>
-      <c r="I80" t="s">
-        <v>203</v>
-      </c>
-      <c r="K80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>11</v>
-      </c>
-      <c r="B81" t="s">
-        <v>113</v>
-      </c>
-      <c r="C81" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" t="s">
-        <v>104</v>
-      </c>
-      <c r="G81" t="s">
-        <v>104</v>
-      </c>
-      <c r="H81" t="s">
-        <v>115</v>
-      </c>
-      <c r="K81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>11</v>
-      </c>
-      <c r="B82" t="s">
-        <v>116</v>
-      </c>
-      <c r="C82" t="s">
-        <v>117</v>
-      </c>
-      <c r="E82" t="s">
-        <v>104</v>
-      </c>
-      <c r="G82" t="s">
-        <v>104</v>
-      </c>
-      <c r="H82" t="s">
-        <v>118</v>
-      </c>
-      <c r="K82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>11</v>
-      </c>
-      <c r="B83" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" t="s">
-        <v>120</v>
-      </c>
-      <c r="E83" t="s">
-        <v>104</v>
-      </c>
-      <c r="G83" t="s">
-        <v>104</v>
-      </c>
-      <c r="H83" t="s">
-        <v>121</v>
-      </c>
-      <c r="K83" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" t="s">
-        <v>399</v>
-      </c>
-      <c r="C84" t="s">
-        <v>285</v>
-      </c>
-      <c r="E84" t="s">
-        <v>166</v>
-      </c>
-      <c r="G84" t="s">
-        <v>166</v>
-      </c>
-      <c r="I84" t="s">
-        <v>200</v>
-      </c>
-      <c r="K84" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B85" t="s">
-        <v>398</v>
-      </c>
-      <c r="C85" t="s">
-        <v>284</v>
-      </c>
-      <c r="E85" t="s">
-        <v>166</v>
-      </c>
-      <c r="G85" t="s">
-        <v>166</v>
-      </c>
-      <c r="I85" t="s">
-        <v>200</v>
-      </c>
-      <c r="K85" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B86" t="s">
-        <v>400</v>
-      </c>
-      <c r="C86" t="s">
-        <v>286</v>
-      </c>
-      <c r="E86" t="s">
-        <v>166</v>
-      </c>
-      <c r="G86" t="s">
-        <v>166</v>
-      </c>
-      <c r="I86" t="s">
-        <v>200</v>
-      </c>
-      <c r="K86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" t="s">
-        <v>356</v>
-      </c>
-      <c r="C87" t="s">
-        <v>248</v>
-      </c>
-      <c r="E87" t="s">
-        <v>166</v>
-      </c>
-      <c r="G87" t="s">
-        <v>166</v>
-      </c>
-      <c r="I87" t="s">
-        <v>203</v>
-      </c>
-      <c r="K87" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" t="s">
-        <v>446</v>
-      </c>
-      <c r="C88" t="s">
-        <v>447</v>
-      </c>
-      <c r="E88" t="s">
-        <v>170</v>
-      </c>
-      <c r="I88" t="s">
-        <v>448</v>
-      </c>
-      <c r="K88" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>11</v>
-      </c>
-      <c r="B89" t="s">
-        <v>341</v>
-      </c>
-      <c r="C89" t="s">
-        <v>233</v>
-      </c>
-      <c r="E89" t="s">
-        <v>166</v>
-      </c>
-      <c r="G89" t="s">
-        <v>166</v>
-      </c>
-      <c r="I89" t="s">
-        <v>203</v>
-      </c>
-      <c r="K89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90" t="s">
-        <v>492</v>
-      </c>
-      <c r="C90" t="s">
-        <v>493</v>
-      </c>
-      <c r="E90" t="s">
-        <v>104</v>
-      </c>
-      <c r="I90" t="s">
-        <v>448</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>11</v>
-      </c>
-      <c r="B91" t="s">
-        <v>346</v>
-      </c>
-      <c r="C91" t="s">
-        <v>238</v>
-      </c>
-      <c r="E91" t="s">
-        <v>166</v>
-      </c>
-      <c r="G91" t="s">
-        <v>166</v>
-      </c>
-      <c r="I91" t="s">
-        <v>203</v>
-      </c>
-      <c r="K91" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>11</v>
-      </c>
-      <c r="B92" t="s">
-        <v>387</v>
-      </c>
-      <c r="C92" t="s">
-        <v>269</v>
-      </c>
-      <c r="E92" t="s">
-        <v>166</v>
-      </c>
-      <c r="G92" t="s">
-        <v>166</v>
-      </c>
-      <c r="I92" t="s">
-        <v>200</v>
-      </c>
-      <c r="K92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B93" t="s">
-        <v>173</v>
-      </c>
-      <c r="C93" t="s">
-        <v>47</v>
-      </c>
-      <c r="E93" t="s">
-        <v>46</v>
-      </c>
-      <c r="G93" t="s">
-        <v>38</v>
-      </c>
-      <c r="H93" t="s">
-        <v>46</v>
-      </c>
-      <c r="K93" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>11</v>
-      </c>
-      <c r="B94" t="s">
-        <v>371</v>
-      </c>
-      <c r="C94" t="s">
-        <v>264</v>
-      </c>
-      <c r="E94" t="s">
-        <v>166</v>
-      </c>
-      <c r="G94" t="s">
-        <v>166</v>
-      </c>
-      <c r="I94" t="s">
-        <v>203</v>
-      </c>
-      <c r="K94" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>11</v>
-      </c>
-      <c r="B95" t="s">
-        <v>43</v>
-      </c>
-      <c r="C95" t="s">
-        <v>44</v>
-      </c>
-      <c r="E95" t="s">
-        <v>38</v>
-      </c>
-      <c r="G95" t="s">
-        <v>38</v>
-      </c>
-      <c r="H95" t="s">
-        <v>16</v>
-      </c>
-      <c r="K95" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>11</v>
-      </c>
-      <c r="B96" t="s">
-        <v>717</v>
-      </c>
-      <c r="C96" t="s">
-        <v>211</v>
-      </c>
-      <c r="E96" t="s">
-        <v>166</v>
-      </c>
-      <c r="G96" t="s">
-        <v>166</v>
-      </c>
-      <c r="I96" t="s">
-        <v>554</v>
-      </c>
-      <c r="K96" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>11</v>
-      </c>
-      <c r="B97" t="s">
-        <v>367</v>
-      </c>
-      <c r="C97" t="s">
-        <v>260</v>
-      </c>
-      <c r="E97" t="s">
-        <v>166</v>
-      </c>
-      <c r="G97" t="s">
-        <v>166</v>
-      </c>
-      <c r="I97" t="s">
-        <v>203</v>
-      </c>
-      <c r="K97" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="K98" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>11</v>
-      </c>
-      <c r="B101" t="s">
-        <v>334</v>
-      </c>
-      <c r="C101" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" t="s">
-        <v>166</v>
-      </c>
-      <c r="G101" t="s">
-        <v>166</v>
-      </c>
-      <c r="I101" t="s">
-        <v>203</v>
-      </c>
-      <c r="K101" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102" t="s">
-        <v>409</v>
-      </c>
-      <c r="C102" t="s">
-        <v>192</v>
-      </c>
-      <c r="E102" t="s">
-        <v>167</v>
-      </c>
-      <c r="G102" t="s">
-        <v>167</v>
-      </c>
-      <c r="I102" t="s">
-        <v>188</v>
-      </c>
-      <c r="K102" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>11</v>
-      </c>
-      <c r="B103" t="s">
-        <v>328</v>
-      </c>
-      <c r="C103" t="s">
-        <v>218</v>
-      </c>
-      <c r="E103" t="s">
-        <v>166</v>
-      </c>
-      <c r="G103" t="s">
-        <v>166</v>
-      </c>
-      <c r="I103" t="s">
-        <v>203</v>
-      </c>
-      <c r="K103" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>11</v>
-      </c>
-      <c r="B104" t="s">
-        <v>77</v>
-      </c>
-      <c r="C104" t="s">
-        <v>78</v>
-      </c>
-      <c r="E104" t="s">
-        <v>76</v>
-      </c>
-      <c r="G104" t="s">
-        <v>76</v>
-      </c>
-      <c r="H104" t="s">
-        <v>16</v>
-      </c>
-      <c r="K104" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>11</v>
-      </c>
-      <c r="B105" t="s">
-        <v>435</v>
-      </c>
-      <c r="C105" t="s">
-        <v>726</v>
-      </c>
-      <c r="E105" t="s">
-        <v>170</v>
-      </c>
-      <c r="G105" t="s">
-        <v>171</v>
-      </c>
-      <c r="I105" t="s">
-        <v>188</v>
-      </c>
-      <c r="K105" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>